--- a/Vorlage.xlsx
+++ b/Vorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\diNo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\diNo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02242AAE-7E8D-4831-8771-8CD5AB8E955F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87379467-05F2-4820-B90C-59238C23075D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="873" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Halbjahr" sheetId="1" r:id="rId1"/>
@@ -60,19 +60,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="20">'Eingabe Abitur'!$1:$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -136,14 +123,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -3713,6 +3700,52 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
@@ -3765,42 +3798,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
@@ -3834,6 +3831,14 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -3879,10 +3884,29 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3917,25 +3941,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="3" applyBorder="1" applyAlignment="1">
@@ -3980,17 +3985,20 @@
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="93" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="94" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="82" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4013,50 +4021,6 @@
     <xf numFmtId="1" fontId="19" fillId="0" borderId="84" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="85" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="93" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="82" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4082,23 +4046,46 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="85" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="93" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="93" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="94" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4749,9 +4736,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4789,9 +4776,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4824,9 +4811,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4859,9 +4863,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5069,24 +5090,24 @@
         <v>33</v>
       </c>
       <c r="D1" s="190"/>
-      <c r="E1" s="468"/>
-      <c r="F1" s="468"/>
-      <c r="G1" s="468"/>
-      <c r="H1" s="469"/>
-      <c r="I1" s="466" t="s">
+      <c r="E1" s="455"/>
+      <c r="F1" s="455"/>
+      <c r="G1" s="455"/>
+      <c r="H1" s="456"/>
+      <c r="I1" s="453" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="467"/>
-      <c r="K1" s="470"/>
-      <c r="L1" s="471"/>
+      <c r="J1" s="454"/>
+      <c r="K1" s="457"/>
+      <c r="L1" s="458"/>
       <c r="M1" s="386" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="462">
+      <c r="N1" s="449">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
-      </c>
-      <c r="O1" s="463"/>
+        <v>46296</v>
+      </c>
+      <c r="O1" s="450"/>
       <c r="P1" s="384"/>
       <c r="Q1" s="384"/>
       <c r="R1" s="384"/>
@@ -5113,21 +5134,21 @@
       <c r="B2" s="123" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="464" t="s">
+      <c r="C2" s="451" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="465"/>
-      <c r="E2" s="465"/>
-      <c r="F2" s="465"/>
-      <c r="G2" s="465"/>
-      <c r="H2" s="465"/>
-      <c r="I2" s="465"/>
-      <c r="J2" s="465"/>
-      <c r="K2" s="465"/>
-      <c r="L2" s="465"/>
-      <c r="M2" s="465"/>
-      <c r="N2" s="465"/>
-      <c r="O2" s="465"/>
+      <c r="D2" s="452"/>
+      <c r="E2" s="452"/>
+      <c r="F2" s="452"/>
+      <c r="G2" s="452"/>
+      <c r="H2" s="452"/>
+      <c r="I2" s="452"/>
+      <c r="J2" s="452"/>
+      <c r="K2" s="452"/>
+      <c r="L2" s="452"/>
+      <c r="M2" s="452"/>
+      <c r="N2" s="452"/>
+      <c r="O2" s="452"/>
       <c r="P2" s="384"/>
       <c r="Q2" s="384"/>
       <c r="R2" s="384"/>
@@ -9678,17 +9699,17 @@
       <c r="B1" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -9804,11 +9825,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -11122,48 +11143,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -11582,17 +11603,17 @@
       <c r="B1" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -11708,11 +11729,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -13026,48 +13047,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -13486,17 +13507,17 @@
       <c r="B1" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -13612,11 +13633,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -14930,48 +14951,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -15390,17 +15411,17 @@
       <c r="B1" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -15516,11 +15537,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -16834,48 +16855,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -17294,17 +17315,17 @@
       <c r="B1" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -17420,11 +17441,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -18738,48 +18759,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -19198,17 +19219,17 @@
       <c r="B1" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -19324,11 +19345,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -20642,48 +20663,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -21102,17 +21123,17 @@
       <c r="B1" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -21228,11 +21249,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -22546,48 +22567,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -23007,10 +23028,10 @@
         <f>"Fach: "&amp;'1. Halbjahr'!E1</f>
         <v xml:space="preserve">Fach: </v>
       </c>
-      <c r="E2" s="484"/>
-      <c r="F2" s="484"/>
-      <c r="G2" s="484"/>
-      <c r="H2" s="484"/>
+      <c r="E2" s="489"/>
+      <c r="F2" s="489"/>
+      <c r="G2" s="489"/>
+      <c r="H2" s="489"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="str">
@@ -23060,20 +23081,20 @@
     <row r="5" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="328"/>
-      <c r="C5" s="485"/>
-      <c r="D5" s="485"/>
-      <c r="E5" s="486"/>
-      <c r="F5" s="482" t="s">
+      <c r="C5" s="490"/>
+      <c r="D5" s="490"/>
+      <c r="E5" s="491"/>
+      <c r="F5" s="487" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="483"/>
+      <c r="G5" s="488"/>
       <c r="H5" s="394" t="s">
         <v>107</v>
       </c>
-      <c r="I5" s="487" t="s">
+      <c r="I5" s="492" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="488"/>
+      <c r="J5" s="493"/>
       <c r="K5" s="348" t="s">
         <v>12</v>
       </c>
@@ -23081,14 +23102,14 @@
       <c r="N5"/>
       <c r="O5" s="155">
         <f>IF($E$43="M", $I$44+11*(100-$I$44)/12, $I$44+27*(100-$I$44)/30)</f>
-        <v>95</v>
+        <v>94.916666666666657</v>
       </c>
       <c r="P5" s="56">
         <v>15</v>
       </c>
       <c r="Q5" s="156">
         <f>(O5-100*SUM($D$50:D50)/$E$44)</f>
-        <v>95</v>
+        <v>94.916666666666657</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
@@ -23134,14 +23155,14 @@
       <c r="N6"/>
       <c r="O6" s="155">
         <f>IF($E$43="M", $I$44+10*(100-$I$44)/12,$I$44+24*(100-$I$44)/30)</f>
-        <v>90</v>
+        <v>89.833333333333343</v>
       </c>
       <c r="P6" s="56">
         <v>14</v>
       </c>
       <c r="Q6" s="156">
         <f>(O6-100*SUM($D$50:D51)/$E$44)</f>
-        <v>90</v>
+        <v>89.833333333333343</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -23187,14 +23208,14 @@
       <c r="N7"/>
       <c r="O7" s="155">
         <f>IF($E$43="M", $I$44+9*(100-$I$44)/12, $I$44+21*(100-$I$44)/30)</f>
-        <v>85</v>
+        <v>84.75</v>
       </c>
       <c r="P7" s="56">
         <v>13</v>
       </c>
       <c r="Q7" s="156">
         <f>(O7-100*SUM($D$50:D52)/$E$44)</f>
-        <v>85</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -23240,14 +23261,14 @@
       <c r="N8"/>
       <c r="O8" s="155">
         <f>IF($E$43="M", $I$44+8*(100-$I$44)/12,$I$44+18*(100-$I$44)/30)</f>
-        <v>80</v>
+        <v>79.666666666666657</v>
       </c>
       <c r="P8" s="56">
         <v>12</v>
       </c>
       <c r="Q8" s="156">
         <f>(O8-100*SUM($D$50:D53)/$E$44)</f>
-        <v>80</v>
+        <v>79.666666666666657</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
@@ -23293,14 +23314,14 @@
       <c r="N9"/>
       <c r="O9" s="155">
         <f>IF($E$43="M", $I$44+7*(100-$I$44)/12, $I$44+15*(100-$I$44)/30)</f>
-        <v>75</v>
+        <v>74.583333333333343</v>
       </c>
       <c r="P9" s="56">
         <v>11</v>
       </c>
       <c r="Q9" s="156">
         <f>(O9-100*SUM($D$50:D54)/$E$44)</f>
-        <v>75</v>
+        <v>74.583333333333343</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
@@ -23346,14 +23367,14 @@
       <c r="N10"/>
       <c r="O10" s="155">
         <f>IF($E$43="M", $I$44+6*(100-$I$44)/12, $I$44+12*(100-$I$44)/30)</f>
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="P10" s="56">
         <v>10</v>
       </c>
       <c r="Q10" s="156">
         <f>(O10-100*SUM($D$50:D55)/$E$44)</f>
-        <v>70</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -23399,14 +23420,14 @@
       <c r="N11"/>
       <c r="O11" s="155">
         <f>IF($E$43="M", $I$44+5*(100-$I$44)/12, $I$44+10*(100-$I$44)/30)</f>
-        <v>65</v>
+        <v>64.416666666666671</v>
       </c>
       <c r="P11" s="56">
         <v>9</v>
       </c>
       <c r="Q11" s="156">
         <f>(O11-100*SUM($D$50:D56)/$E$44)</f>
-        <v>65</v>
+        <v>64.416666666666671</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -23452,14 +23473,14 @@
       <c r="N12"/>
       <c r="O12" s="155">
         <f>IF($E$43="M", $I$44+4*(100-$I$44)/12, $I$44+8*(100-$I$44)/30)</f>
-        <v>60</v>
+        <v>59.333333333333329</v>
       </c>
       <c r="P12" s="56">
         <v>8</v>
       </c>
       <c r="Q12" s="156">
         <f>(O12-100*SUM($D$50:D57)/$E$44)</f>
-        <v>60</v>
+        <v>59.333333333333329</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
@@ -23505,14 +23526,14 @@
       <c r="N13"/>
       <c r="O13" s="155">
         <f>IF($E$43="M", $I$44+3*(100-$I$44)/12, $I$44+6*(100-$I$44)/30)</f>
-        <v>55</v>
+        <v>54.25</v>
       </c>
       <c r="P13" s="56">
         <v>7</v>
       </c>
       <c r="Q13" s="156">
         <f>(O13-100*SUM($D$50:D58)/$E$44)</f>
-        <v>55</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -23558,14 +23579,14 @@
       <c r="N14"/>
       <c r="O14" s="155">
         <f>IF($E$43="M", $I$44+2*(100-$I$44)/12, $I$44+4*(100-$I$44)/30)</f>
-        <v>50</v>
+        <v>49.166666666666664</v>
       </c>
       <c r="P14" s="56">
         <v>6</v>
       </c>
       <c r="Q14" s="156">
         <f>(O14-100*SUM($D$50:D59)/$E$44)</f>
-        <v>50</v>
+        <v>49.166666666666664</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
@@ -23611,14 +23632,14 @@
       <c r="N15"/>
       <c r="O15" s="155">
         <f>IF($E$43="M",$I$44+1*(100-$I$44)/12, $I$44+2*(100-$I$44)/30)</f>
-        <v>45</v>
+        <v>44.083333333333336</v>
       </c>
       <c r="P15" s="56">
         <v>5</v>
       </c>
       <c r="Q15" s="156">
         <f>(O15-100*SUM($D$50:D60)/$E$44)</f>
-        <v>45</v>
+        <v>44.083333333333336</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -23664,14 +23685,14 @@
       <c r="N16"/>
       <c r="O16" s="155">
         <f>$I$44</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P16" s="56">
         <v>4</v>
       </c>
       <c r="Q16" s="156">
         <f>(O16-100*SUM($D$50:D61)/$E$44)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
@@ -23717,14 +23738,14 @@
       <c r="N17"/>
       <c r="O17" s="155">
         <f>($G$44+2*($I$44-$G$44)/3)</f>
-        <v>33.333333333333336</v>
+        <v>32.666666666666664</v>
       </c>
       <c r="P17" s="56">
         <v>3</v>
       </c>
       <c r="Q17" s="156">
         <f>(O17-100*SUM($D$50:D62)/$E$44)</f>
-        <v>33.333333333333336</v>
+        <v>32.666666666666664</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
@@ -23770,14 +23791,14 @@
       <c r="N18"/>
       <c r="O18" s="155">
         <f>($G$44+($I$44-$G$44)/3)</f>
-        <v>26.666666666666668</v>
+        <v>26.333333333333332</v>
       </c>
       <c r="P18" s="56">
         <v>2</v>
       </c>
       <c r="Q18" s="156">
         <f>(O18-100*SUM($D$50:D63)/$E$44)</f>
-        <v>26.666666666666668</v>
+        <v>26.333333333333332</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
@@ -24739,11 +24760,11 @@
       <c r="E43" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="481" t="s">
+      <c r="G43" s="486" t="s">
         <v>38</v>
       </c>
-      <c r="H43" s="481"/>
-      <c r="I43" s="481"/>
+      <c r="H43" s="486"/>
+      <c r="I43" s="486"/>
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
@@ -24763,7 +24784,7 @@
         <v>37</v>
       </c>
       <c r="I44" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J44" s="59"/>
     </row>
@@ -24816,7 +24837,7 @@
       </c>
       <c r="F50" s="160">
         <f>E51+0.5</f>
-        <v>95.5</v>
+        <v>94.5</v>
       </c>
       <c r="G50" s="206">
         <v>15</v>
@@ -24835,11 +24856,11 @@
     <row r="51" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E51" s="358">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F51" s="158">
         <f t="shared" ref="F51:F63" si="5">E52+0.5</f>
-        <v>90.5</v>
+        <v>89.5</v>
       </c>
       <c r="G51" s="207">
         <v>14</v>
@@ -24864,11 +24885,11 @@
     <row r="52" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E52" s="360">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F52" s="161">
         <f t="shared" si="5"/>
-        <v>85.5</v>
+        <v>84.5</v>
       </c>
       <c r="G52" s="208">
         <v>13</v>
@@ -24887,11 +24908,11 @@
     <row r="53" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E53" s="359">
         <f t="shared" si="4"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F53" s="160">
         <f t="shared" si="5"/>
-        <v>80.5</v>
+        <v>79.5</v>
       </c>
       <c r="G53" s="207">
         <v>12</v>
@@ -24910,11 +24931,11 @@
     <row r="54" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E54" s="358">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F54" s="158">
         <f t="shared" si="5"/>
-        <v>75.5</v>
+        <v>74.5</v>
       </c>
       <c r="G54" s="207">
         <v>11</v>
@@ -24939,11 +24960,11 @@
     <row r="55" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E55" s="360">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F55" s="161">
         <f t="shared" si="5"/>
-        <v>70.5</v>
+        <v>69.5</v>
       </c>
       <c r="G55" s="207">
         <v>10</v>
@@ -24962,11 +24983,11 @@
     <row r="56" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E56" s="358">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F56" s="160">
         <f t="shared" si="5"/>
-        <v>65.5</v>
+        <v>64.5</v>
       </c>
       <c r="G56" s="206">
         <v>9</v>
@@ -24985,11 +25006,11 @@
     <row r="57" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E57" s="358">
         <f t="shared" si="4"/>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F57" s="158">
         <f t="shared" si="5"/>
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="G57" s="207">
         <v>8</v>
@@ -25014,11 +25035,11 @@
     <row r="58" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E58" s="360">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="161">
         <f t="shared" si="5"/>
-        <v>55.5</v>
+        <v>54.5</v>
       </c>
       <c r="G58" s="208">
         <v>7</v>
@@ -25037,11 +25058,11 @@
     <row r="59" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E59" s="358">
         <f t="shared" si="4"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F59" s="160">
         <f t="shared" si="5"/>
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="G59" s="207">
         <v>6</v>
@@ -25060,11 +25081,11 @@
     <row r="60" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E60" s="358">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F60" s="158">
         <f t="shared" si="5"/>
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
       <c r="G60" s="207">
         <v>5</v>
@@ -25089,11 +25110,11 @@
     <row r="61" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E61" s="360">
         <f t="shared" si="4"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F61" s="161">
         <f t="shared" si="5"/>
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="G61" s="207">
         <v>4</v>
@@ -25112,11 +25133,11 @@
     <row r="62" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E62" s="358">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F62" s="160">
         <f t="shared" si="5"/>
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
       <c r="G62" s="206">
         <v>3</v>
@@ -25135,7 +25156,7 @@
     <row r="63" spans="4:12" x14ac:dyDescent="0.2">
       <c r="E63" s="358">
         <f t="shared" si="4"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F63" s="158">
         <f t="shared" si="5"/>
@@ -25351,14 +25372,14 @@
       <c r="AD3" s="405"/>
       <c r="AE3" s="404"/>
       <c r="AF3" s="405"/>
-      <c r="AG3" s="489" t="s">
+      <c r="AG3" s="494" t="s">
         <v>118</v>
       </c>
-      <c r="AH3" s="490"/>
-      <c r="AI3" s="491" t="s">
+      <c r="AH3" s="495"/>
+      <c r="AI3" s="496" t="s">
         <v>63</v>
       </c>
-      <c r="AJ3" s="492"/>
+      <c r="AJ3" s="497"/>
     </row>
     <row r="4" spans="1:36" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="372"/>
@@ -27586,15 +27607,15 @@
       <c r="G5" s="100"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="507" t="s">
+      <c r="A7" s="498" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="508"/>
-      <c r="C7" s="508"/>
-      <c r="D7" s="508"/>
-      <c r="E7" s="508"/>
-      <c r="F7" s="508"/>
-      <c r="G7" s="509"/>
+      <c r="B7" s="499"/>
+      <c r="C7" s="499"/>
+      <c r="D7" s="499"/>
+      <c r="E7" s="499"/>
+      <c r="F7" s="499"/>
+      <c r="G7" s="500"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="101"/>
@@ -27610,14 +27631,14 @@
       <c r="B9" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="510" t="s">
+      <c r="C9" s="501" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="510"/>
-      <c r="E9" s="512" t="s">
+      <c r="D9" s="501"/>
+      <c r="E9" s="505" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="513"/>
+      <c r="F9" s="506"/>
       <c r="G9" s="89"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -28656,8 +28677,8 @@
       <c r="C46" s="106"/>
     </row>
     <row r="47" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="511"/>
-      <c r="B47" s="511"/>
+      <c r="A47" s="502"/>
+      <c r="B47" s="502"/>
       <c r="C47" s="107" t="s">
         <v>52</v>
       </c>
@@ -28673,13 +28694,13 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="493">
+      <c r="A48" s="503">
         <v>15</v>
       </c>
-      <c r="B48" s="494"/>
+      <c r="B48" s="504"/>
       <c r="C48" s="109" t="str">
         <f>AP!E50 &amp;"-"&amp; AP!F50</f>
-        <v>100-95,5</v>
+        <v>100-94,5</v>
       </c>
       <c r="D48" s="109">
         <f t="shared" ref="D48:D55" ca="1" si="1">COUNTIF($E$11:$E$45,A48)</f>
@@ -28690,7 +28711,7 @@
       </c>
       <c r="F48" s="109" t="str">
         <f>AP!E58 &amp;"-"&amp; AP!F58</f>
-        <v>60-55,5</v>
+        <v>59-54,5</v>
       </c>
       <c r="G48" s="109">
         <f t="shared" ref="G48:G55" ca="1" si="2">COUNTIF($E$11:$E$45,E48)</f>
@@ -28698,13 +28719,13 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="493">
+      <c r="A49" s="503">
         <v>14</v>
       </c>
-      <c r="B49" s="494"/>
+      <c r="B49" s="504"/>
       <c r="C49" s="109" t="str">
         <f>AP!E51 &amp;"-"&amp; AP!F51</f>
-        <v>95-90,5</v>
+        <v>94-89,5</v>
       </c>
       <c r="D49" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28715,7 +28736,7 @@
       </c>
       <c r="F49" s="109" t="str">
         <f>AP!E59 &amp;"-"&amp; AP!F59</f>
-        <v>55-50,5</v>
+        <v>54-49,5</v>
       </c>
       <c r="G49" s="109">
         <f t="shared" ca="1" si="2"/>
@@ -28723,13 +28744,13 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="493">
+      <c r="A50" s="503">
         <v>13</v>
       </c>
-      <c r="B50" s="494"/>
+      <c r="B50" s="504"/>
       <c r="C50" s="109" t="str">
         <f>AP!E52 &amp;"-"&amp; AP!F52</f>
-        <v>90-85,5</v>
+        <v>89-84,5</v>
       </c>
       <c r="D50" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28740,7 +28761,7 @@
       </c>
       <c r="F50" s="109" t="str">
         <f>AP!E60 &amp;"-"&amp; AP!F60</f>
-        <v>50-45,5</v>
+        <v>49-44,5</v>
       </c>
       <c r="G50" s="109">
         <f t="shared" ca="1" si="2"/>
@@ -28748,13 +28769,13 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="493">
+      <c r="A51" s="503">
         <v>12</v>
       </c>
-      <c r="B51" s="494"/>
+      <c r="B51" s="504"/>
       <c r="C51" s="109" t="str">
         <f>AP!E53 &amp;"-"&amp; AP!F53</f>
-        <v>85-80,5</v>
+        <v>84-79,5</v>
       </c>
       <c r="D51" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28765,7 +28786,7 @@
       </c>
       <c r="F51" s="109" t="str">
         <f>AP!E61 &amp;"-"&amp; AP!F61</f>
-        <v>45-40,5</v>
+        <v>44-39,5</v>
       </c>
       <c r="G51" s="109">
         <f t="shared" ca="1" si="2"/>
@@ -28773,13 +28794,13 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="493">
+      <c r="A52" s="503">
         <v>11</v>
       </c>
-      <c r="B52" s="494"/>
+      <c r="B52" s="504"/>
       <c r="C52" s="109" t="str">
         <f>AP!E54 &amp;"-"&amp; AP!F54</f>
-        <v>80-75,5</v>
+        <v>79-74,5</v>
       </c>
       <c r="D52" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28790,7 +28811,7 @@
       </c>
       <c r="F52" s="109" t="str">
         <f>AP!E62 &amp;"-"&amp; AP!F62</f>
-        <v>40-33,5</v>
+        <v>39-32,5</v>
       </c>
       <c r="G52" s="109">
         <f t="shared" ca="1" si="2"/>
@@ -28798,13 +28819,13 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="493">
+      <c r="A53" s="503">
         <v>10</v>
       </c>
-      <c r="B53" s="494"/>
+      <c r="B53" s="504"/>
       <c r="C53" s="109" t="str">
         <f>AP!E55 &amp;"-"&amp; AP!F55</f>
-        <v>75-70,5</v>
+        <v>74-69,5</v>
       </c>
       <c r="D53" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28815,7 +28836,7 @@
       </c>
       <c r="F53" s="109" t="str">
         <f>AP!E63 &amp;"-"&amp; AP!F63</f>
-        <v>33-26,5</v>
+        <v>32-26,5</v>
       </c>
       <c r="G53" s="109">
         <f t="shared" ca="1" si="2"/>
@@ -28823,13 +28844,13 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="493">
+      <c r="A54" s="503">
         <v>9</v>
       </c>
-      <c r="B54" s="494"/>
+      <c r="B54" s="504"/>
       <c r="C54" s="109" t="str">
         <f>AP!E56 &amp;"-"&amp; AP!F56</f>
-        <v>70-65,5</v>
+        <v>69-64,5</v>
       </c>
       <c r="D54" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28848,13 +28869,13 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="493">
+      <c r="A55" s="503">
         <v>8</v>
       </c>
-      <c r="B55" s="494"/>
+      <c r="B55" s="504"/>
       <c r="C55" s="109" t="str">
         <f>AP!E57 &amp;"-"&amp; AP!F57</f>
-        <v>65-60,5</v>
+        <v>64-59,5</v>
       </c>
       <c r="D55" s="109">
         <f t="shared" ca="1" si="1"/>
@@ -28877,60 +28898,69 @@
       <c r="G56" s="89"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="504" t="s">
+      <c r="A57" s="516" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="505"/>
-      <c r="C57" s="505"/>
-      <c r="D57" s="505"/>
-      <c r="E57" s="505"/>
-      <c r="F57" s="505"/>
-      <c r="G57" s="506"/>
+      <c r="B57" s="517"/>
+      <c r="C57" s="517"/>
+      <c r="D57" s="517"/>
+      <c r="E57" s="517"/>
+      <c r="F57" s="517"/>
+      <c r="G57" s="518"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="495" t="e">
+      <c r="A58" s="507" t="e">
         <f ca="1">AVERAGE(E11:E45)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="B58" s="496"/>
-      <c r="C58" s="496"/>
-      <c r="D58" s="496"/>
-      <c r="E58" s="496"/>
-      <c r="F58" s="496"/>
-      <c r="G58" s="497"/>
+      <c r="B58" s="508"/>
+      <c r="C58" s="508"/>
+      <c r="D58" s="508"/>
+      <c r="E58" s="508"/>
+      <c r="F58" s="508"/>
+      <c r="G58" s="509"/>
     </row>
     <row r="60" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="501" t="s">
+      <c r="A60" s="513" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="502"/>
-      <c r="C60" s="502"/>
-      <c r="D60" s="502"/>
-      <c r="E60" s="502"/>
-      <c r="F60" s="502"/>
-      <c r="G60" s="503"/>
+      <c r="B60" s="514"/>
+      <c r="C60" s="514"/>
+      <c r="D60" s="514"/>
+      <c r="E60" s="514"/>
+      <c r="F60" s="514"/>
+      <c r="G60" s="515"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="88"/>
-      <c r="B65" s="500"/>
-      <c r="C65" s="500"/>
-      <c r="F65" s="499"/>
-      <c r="G65" s="499"/>
+      <c r="B65" s="512"/>
+      <c r="C65" s="512"/>
+      <c r="F65" s="511"/>
+      <c r="G65" s="511"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B66" s="498" t="s">
+      <c r="B66" s="510" t="s">
         <v>49</v>
       </c>
-      <c r="C66" s="498"/>
+      <c r="C66" s="510"/>
       <c r="E66" s="87"/>
-      <c r="F66" s="498" t="s">
+      <c r="F66" s="510" t="s">
         <v>48</v>
       </c>
-      <c r="G66" s="498"/>
+      <c r="G66" s="510"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wyO6Ez8zhREBMTjktXqbZDsYLF0kp82Zmmqs6at3xZ3VIbPGyjFYc5DwSrjn8KCcXgCrhQhJgbgCd/X3W3qxYQ==" saltValue="RIStUfpXqtccIQ7SE0qNhg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A47:B47"/>
@@ -28941,15 +28971,6 @@
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A57:G57"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0.35433070866141736" top="0.39" bottom="0.52" header="0.19" footer="0.45"/>
@@ -29036,17 +29057,17 @@
       <c r="B1" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -29162,11 +29183,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -30480,48 +30501,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -30976,15 +30997,15 @@
       <c r="G4" s="432"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="515" t="s">
+      <c r="A6" s="520" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="516"/>
-      <c r="C6" s="516"/>
-      <c r="D6" s="516"/>
-      <c r="E6" s="516"/>
-      <c r="F6" s="516"/>
-      <c r="G6" s="517"/>
+      <c r="B6" s="521"/>
+      <c r="C6" s="521"/>
+      <c r="D6" s="521"/>
+      <c r="E6" s="521"/>
+      <c r="F6" s="521"/>
+      <c r="G6" s="522"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="298"/>
@@ -31650,53 +31671,53 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="298"/>
-      <c r="D55" s="518" t="s">
+      <c r="D55" s="523" t="s">
         <v>50</v>
       </c>
-      <c r="E55" s="519"/>
-      <c r="F55" s="519"/>
-      <c r="G55" s="520"/>
+      <c r="E55" s="524"/>
+      <c r="F55" s="524"/>
+      <c r="G55" s="525"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="306"/>
       <c r="B56" s="296"/>
       <c r="C56" s="296"/>
-      <c r="D56" s="521" t="str">
+      <c r="D56" s="526" t="str">
         <f>IF(SUM(C9:C43)=0,"",AVERAGE(C9:C43))</f>
         <v/>
       </c>
-      <c r="E56" s="522"/>
-      <c r="F56" s="522"/>
-      <c r="G56" s="523"/>
+      <c r="E56" s="527"/>
+      <c r="F56" s="527"/>
+      <c r="G56" s="528"/>
     </row>
     <row r="57" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="524" t="s">
+      <c r="A57" s="529" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="525"/>
-      <c r="C57" s="525"/>
-      <c r="D57" s="525"/>
-      <c r="E57" s="525"/>
-      <c r="F57" s="525"/>
-      <c r="G57" s="526"/>
+      <c r="B57" s="530"/>
+      <c r="C57" s="530"/>
+      <c r="D57" s="530"/>
+      <c r="E57" s="530"/>
+      <c r="F57" s="530"/>
+      <c r="G57" s="531"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="527"/>
-      <c r="B59" s="527"/>
+      <c r="A59" s="532"/>
+      <c r="B59" s="532"/>
       <c r="F59" s="307"/>
       <c r="G59" s="307"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="514" t="s">
+      <c r="A60" s="519" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="514"/>
-      <c r="D60" s="514" t="s">
+      <c r="B60" s="519"/>
+      <c r="D60" s="519" t="s">
         <v>48</v>
       </c>
-      <c r="E60" s="514"/>
-      <c r="F60" s="514"/>
-      <c r="G60" s="514"/>
+      <c r="E60" s="519"/>
+      <c r="F60" s="519"/>
+      <c r="G60" s="519"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="jQz01aDgUSQc8WMfZ+A6bgUatsN4pnAu4wB0d2+LRy6eXvksY1WlEpMsaC0+BPUVOfzE9BDeQx8gfKrHOotMhA==" saltValue="Z1Xza/YVhTD5ROkkDuiobQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -31809,64 +31830,64 @@
       <c r="Z5" s="219"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C6" s="551" t="s">
+      <c r="C6" s="544" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="552"/>
-      <c r="E6" s="552"/>
-      <c r="F6" s="552"/>
-      <c r="G6" s="552"/>
-      <c r="H6" s="552"/>
-      <c r="I6" s="552"/>
-      <c r="J6" s="552"/>
-      <c r="K6" s="552"/>
-      <c r="L6" s="552"/>
-      <c r="M6" s="552"/>
-      <c r="N6" s="552"/>
-      <c r="O6" s="552"/>
-      <c r="P6" s="552"/>
-      <c r="Q6" s="552"/>
-      <c r="R6" s="553"/>
-      <c r="S6" s="551" t="s">
+      <c r="D6" s="545"/>
+      <c r="E6" s="545"/>
+      <c r="F6" s="545"/>
+      <c r="G6" s="545"/>
+      <c r="H6" s="545"/>
+      <c r="I6" s="545"/>
+      <c r="J6" s="545"/>
+      <c r="K6" s="545"/>
+      <c r="L6" s="545"/>
+      <c r="M6" s="545"/>
+      <c r="N6" s="545"/>
+      <c r="O6" s="545"/>
+      <c r="P6" s="545"/>
+      <c r="Q6" s="545"/>
+      <c r="R6" s="546"/>
+      <c r="S6" s="544" t="s">
         <v>88</v>
       </c>
-      <c r="T6" s="552"/>
-      <c r="U6" s="552"/>
-      <c r="V6" s="552"/>
-      <c r="W6" s="552"/>
-      <c r="X6" s="553"/>
-      <c r="Y6" s="554" t="s">
+      <c r="T6" s="545"/>
+      <c r="U6" s="545"/>
+      <c r="V6" s="545"/>
+      <c r="W6" s="545"/>
+      <c r="X6" s="546"/>
+      <c r="Y6" s="547" t="s">
         <v>89</v>
       </c>
-      <c r="Z6" s="555"/>
+      <c r="Z6" s="548"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C7" s="556" t="s">
+      <c r="C7" s="549" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="547"/>
-      <c r="E7" s="547"/>
-      <c r="F7" s="547"/>
-      <c r="G7" s="547"/>
-      <c r="H7" s="547"/>
-      <c r="I7" s="547"/>
-      <c r="J7" s="557"/>
-      <c r="K7" s="546" t="s">
+      <c r="D7" s="534"/>
+      <c r="E7" s="534"/>
+      <c r="F7" s="534"/>
+      <c r="G7" s="534"/>
+      <c r="H7" s="534"/>
+      <c r="I7" s="534"/>
+      <c r="J7" s="550"/>
+      <c r="K7" s="533" t="s">
         <v>91</v>
       </c>
-      <c r="L7" s="547"/>
-      <c r="M7" s="547"/>
-      <c r="N7" s="547"/>
-      <c r="O7" s="547"/>
-      <c r="P7" s="557"/>
+      <c r="L7" s="534"/>
+      <c r="M7" s="534"/>
+      <c r="N7" s="534"/>
+      <c r="O7" s="534"/>
+      <c r="P7" s="550"/>
       <c r="Q7" s="222"/>
       <c r="R7" s="223"/>
-      <c r="S7" s="558" t="s">
+      <c r="S7" s="551" t="s">
         <v>92</v>
       </c>
-      <c r="T7" s="549"/>
-      <c r="U7" s="549"/>
-      <c r="V7" s="550"/>
+      <c r="T7" s="536"/>
+      <c r="U7" s="536"/>
+      <c r="V7" s="537"/>
       <c r="W7" s="224"/>
       <c r="X7" s="223"/>
       <c r="Y7" s="225"/>
@@ -31895,15 +31916,15 @@
         <v>93</v>
       </c>
       <c r="J8" s="231"/>
-      <c r="K8" s="546" t="s">
+      <c r="K8" s="533" t="s">
         <v>94</v>
       </c>
-      <c r="L8" s="547"/>
-      <c r="M8" s="548" t="s">
+      <c r="L8" s="534"/>
+      <c r="M8" s="535" t="s">
         <v>95</v>
       </c>
-      <c r="N8" s="549"/>
-      <c r="O8" s="550"/>
+      <c r="N8" s="536"/>
+      <c r="O8" s="537"/>
       <c r="P8" s="231"/>
       <c r="Q8" s="232"/>
       <c r="R8" s="223"/>
@@ -32056,10 +32077,10 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="532">
+      <c r="A11" s="538">
         <v>1</v>
       </c>
-      <c r="B11" s="532" t="str">
+      <c r="B11" s="538" t="str">
         <f>IF('1. Halbjahr'!B4&lt;&gt;"", '1. Halbjahr'!B4, "")</f>
         <v/>
       </c>
@@ -32091,18 +32112,18 @@
         <f ca="1">IF(Q11="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q11/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q11))</f>
         <v/>
       </c>
-      <c r="S11" s="534"/>
-      <c r="T11" s="536"/>
-      <c r="U11" s="538"/>
-      <c r="V11" s="540" t="str">
+      <c r="S11" s="540"/>
+      <c r="T11" s="542"/>
+      <c r="U11" s="552"/>
+      <c r="V11" s="554" t="str">
         <f>IF(B11="","",SUM(S11:U11))</f>
         <v/>
       </c>
-      <c r="W11" s="528" t="str">
+      <c r="W11" s="556" t="str">
         <f>IF(B11="","",IF(ISBLANK(S11),"",IF(AVERAGE(S11:U11)&lt;10,LEFT(AVERAGE(S11:U11),4),LEFT(AVERAGE(S11:U11),5))))</f>
         <v/>
       </c>
-      <c r="X11" s="530" t="str">
+      <c r="X11" s="558" t="str">
         <f>IF(B11="","",IF(W11="","",IF(LEFT(W11,1)="0",0,ROUND(W11,0))))</f>
         <v/>
       </c>
@@ -32117,8 +32138,8 @@
       <c r="AB11" s="267"/>
     </row>
     <row r="12" spans="1:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="533"/>
-      <c r="B12" s="533"/>
+      <c r="A12" s="539"/>
+      <c r="B12" s="539"/>
       <c r="C12" s="268"/>
       <c r="D12" s="268"/>
       <c r="E12" s="268"/>
@@ -32147,12 +32168,12 @@
         <f ca="1">IF(Q12="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q12/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q12))</f>
         <v/>
       </c>
-      <c r="S12" s="535"/>
-      <c r="T12" s="537"/>
-      <c r="U12" s="539"/>
-      <c r="V12" s="541"/>
-      <c r="W12" s="529"/>
-      <c r="X12" s="531"/>
+      <c r="S12" s="541"/>
+      <c r="T12" s="543"/>
+      <c r="U12" s="553"/>
+      <c r="V12" s="555"/>
+      <c r="W12" s="557"/>
+      <c r="X12" s="559"/>
       <c r="Y12" s="274" t="str">
         <f>IF(B11="","",ROUNDUP(AVERAGE(R12,R12,X11),2))</f>
         <v/>
@@ -32163,10 +32184,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="532">
+      <c r="A13" s="538">
         <v>2</v>
       </c>
-      <c r="B13" s="532" t="str">
+      <c r="B13" s="538" t="str">
         <f>IF('1. Halbjahr'!B5&lt;&gt;"", '1. Halbjahr'!B5, "")</f>
         <v/>
       </c>
@@ -32198,18 +32219,18 @@
         <f ca="1">IF(Q13="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q13/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q13))</f>
         <v/>
       </c>
-      <c r="S13" s="534"/>
-      <c r="T13" s="536"/>
-      <c r="U13" s="538"/>
-      <c r="V13" s="540" t="str">
+      <c r="S13" s="540"/>
+      <c r="T13" s="542"/>
+      <c r="U13" s="552"/>
+      <c r="V13" s="554" t="str">
         <f>IF(B13="","",SUM(S13:U13))</f>
         <v/>
       </c>
-      <c r="W13" s="528" t="str">
+      <c r="W13" s="556" t="str">
         <f>IF(B13="","",IF(ISBLANK(S13),"",IF(AVERAGE(S13:U13)&lt;10,LEFT(AVERAGE(S13:U13),4),LEFT(AVERAGE(S13:U13),5))))</f>
         <v/>
       </c>
-      <c r="X13" s="530" t="str">
+      <c r="X13" s="558" t="str">
         <f>IF(B13="","",IF(W13="","",IF(LEFT(W13,1)="0",0,ROUND(W13,0))))</f>
         <v/>
       </c>
@@ -32224,8 +32245,8 @@
       <c r="AA13" s="278"/>
     </row>
     <row r="14" spans="1:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="533"/>
-      <c r="B14" s="533"/>
+      <c r="A14" s="539"/>
+      <c r="B14" s="539"/>
       <c r="C14" s="279"/>
       <c r="D14" s="268"/>
       <c r="E14" s="268"/>
@@ -32254,12 +32275,12 @@
         <f ca="1">IF(Q14="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q14/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q14))</f>
         <v/>
       </c>
-      <c r="S14" s="535"/>
-      <c r="T14" s="537"/>
-      <c r="U14" s="539"/>
-      <c r="V14" s="541"/>
-      <c r="W14" s="529"/>
-      <c r="X14" s="531"/>
+      <c r="S14" s="541"/>
+      <c r="T14" s="543"/>
+      <c r="U14" s="553"/>
+      <c r="V14" s="555"/>
+      <c r="W14" s="557"/>
+      <c r="X14" s="559"/>
       <c r="Y14" s="274" t="str">
         <f>IF(B13="","",ROUNDUP(AVERAGE(R14,R14,X13),2))</f>
         <v/>
@@ -32270,10 +32291,10 @@
       </c>
     </row>
     <row r="15" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="532">
+      <c r="A15" s="538">
         <v>3</v>
       </c>
-      <c r="B15" s="532" t="str">
+      <c r="B15" s="538" t="str">
         <f>IF('1. Halbjahr'!B6&lt;&gt;"", '1. Halbjahr'!B6, "")</f>
         <v/>
       </c>
@@ -32305,18 +32326,18 @@
         <f ca="1">IF(Q15="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q15/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q15))</f>
         <v/>
       </c>
-      <c r="S15" s="534"/>
-      <c r="T15" s="536"/>
-      <c r="U15" s="538"/>
-      <c r="V15" s="540" t="str">
+      <c r="S15" s="540"/>
+      <c r="T15" s="542"/>
+      <c r="U15" s="552"/>
+      <c r="V15" s="554" t="str">
         <f>IF(B15="","",SUM(S15:U15))</f>
         <v/>
       </c>
-      <c r="W15" s="528" t="str">
+      <c r="W15" s="556" t="str">
         <f>IF(B15="","",IF(ISBLANK(S15),"",IF(AVERAGE(S15:U15)&lt;10,LEFT(AVERAGE(S15:U15),4),LEFT(AVERAGE(S15:U15),5))))</f>
         <v/>
       </c>
-      <c r="X15" s="530" t="str">
+      <c r="X15" s="558" t="str">
         <f>IF(B15="","",IF(W15="","",IF(LEFT(W15,1)="0",0,ROUND(W15,0))))</f>
         <v/>
       </c>
@@ -32330,8 +32351,8 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="533"/>
-      <c r="B16" s="533"/>
+      <c r="A16" s="539"/>
+      <c r="B16" s="539"/>
       <c r="C16" s="279"/>
       <c r="D16" s="268"/>
       <c r="E16" s="268"/>
@@ -32360,12 +32381,12 @@
         <f ca="1">IF(Q16="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q16/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q16))</f>
         <v/>
       </c>
-      <c r="S16" s="535"/>
-      <c r="T16" s="537"/>
-      <c r="U16" s="539"/>
-      <c r="V16" s="541"/>
-      <c r="W16" s="529"/>
-      <c r="X16" s="531"/>
+      <c r="S16" s="541"/>
+      <c r="T16" s="543"/>
+      <c r="U16" s="553"/>
+      <c r="V16" s="555"/>
+      <c r="W16" s="557"/>
+      <c r="X16" s="559"/>
       <c r="Y16" s="274" t="str">
         <f>IF(B15="","",ROUNDUP(AVERAGE(R16,R16,X15),2))</f>
         <v/>
@@ -32376,10 +32397,10 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="532">
+      <c r="A17" s="538">
         <v>4</v>
       </c>
-      <c r="B17" s="532" t="str">
+      <c r="B17" s="538" t="str">
         <f>IF('1. Halbjahr'!B7&lt;&gt;"", '1. Halbjahr'!B7, "")</f>
         <v/>
       </c>
@@ -32411,18 +32432,18 @@
         <f ca="1">IF(Q17="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q17/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q17))</f>
         <v/>
       </c>
-      <c r="S17" s="534"/>
-      <c r="T17" s="536"/>
-      <c r="U17" s="538"/>
-      <c r="V17" s="540" t="str">
+      <c r="S17" s="540"/>
+      <c r="T17" s="542"/>
+      <c r="U17" s="552"/>
+      <c r="V17" s="554" t="str">
         <f>IF(B17="","",SUM(S17:U17))</f>
         <v/>
       </c>
-      <c r="W17" s="528" t="str">
+      <c r="W17" s="556" t="str">
         <f>IF(B17="","",IF(ISBLANK(S17),"",IF(AVERAGE(S17:U17)&lt;10,LEFT(AVERAGE(S17:U17),4),LEFT(AVERAGE(S17:U17),5))))</f>
         <v/>
       </c>
-      <c r="X17" s="530" t="str">
+      <c r="X17" s="558" t="str">
         <f>IF(B17="","",IF(W17="","",IF(LEFT(W17,1)="0",0,ROUND(W17,0))))</f>
         <v/>
       </c>
@@ -32436,8 +32457,8 @@
       </c>
     </row>
     <row r="18" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="533"/>
-      <c r="B18" s="533"/>
+      <c r="A18" s="539"/>
+      <c r="B18" s="539"/>
       <c r="C18" s="279"/>
       <c r="D18" s="268"/>
       <c r="E18" s="268"/>
@@ -32466,12 +32487,12 @@
         <f ca="1">IF(Q18="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q18/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q18))</f>
         <v/>
       </c>
-      <c r="S18" s="535"/>
-      <c r="T18" s="537"/>
-      <c r="U18" s="539"/>
-      <c r="V18" s="541"/>
-      <c r="W18" s="529"/>
-      <c r="X18" s="531"/>
+      <c r="S18" s="541"/>
+      <c r="T18" s="543"/>
+      <c r="U18" s="553"/>
+      <c r="V18" s="555"/>
+      <c r="W18" s="557"/>
+      <c r="X18" s="559"/>
       <c r="Y18" s="274" t="str">
         <f>IF(B17="","",ROUNDUP(AVERAGE(R18,R18,X17),2))</f>
         <v/>
@@ -32482,10 +32503,10 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="532">
+      <c r="A19" s="538">
         <v>5</v>
       </c>
-      <c r="B19" s="532" t="str">
+      <c r="B19" s="538" t="str">
         <f>IF('1. Halbjahr'!B8&lt;&gt;"", '1. Halbjahr'!B8, "")</f>
         <v/>
       </c>
@@ -32517,18 +32538,18 @@
         <f ca="1">IF(Q19="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q19/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q19))</f>
         <v/>
       </c>
-      <c r="S19" s="534"/>
-      <c r="T19" s="536"/>
-      <c r="U19" s="538"/>
-      <c r="V19" s="540" t="str">
+      <c r="S19" s="540"/>
+      <c r="T19" s="542"/>
+      <c r="U19" s="552"/>
+      <c r="V19" s="554" t="str">
         <f>IF(B19="","",SUM(S19:U19))</f>
         <v/>
       </c>
-      <c r="W19" s="528" t="str">
+      <c r="W19" s="556" t="str">
         <f>IF(B19="","",IF(ISBLANK(S19),"",IF(AVERAGE(S19:U19)&lt;10,LEFT(AVERAGE(S19:U19),4),LEFT(AVERAGE(S19:U19),5))))</f>
         <v/>
       </c>
-      <c r="X19" s="530" t="str">
+      <c r="X19" s="558" t="str">
         <f>IF(B19="","",IF(W19="","",IF(LEFT(W19,1)="0",0,ROUND(W19,0))))</f>
         <v/>
       </c>
@@ -32542,8 +32563,8 @@
       </c>
     </row>
     <row r="20" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="533"/>
-      <c r="B20" s="533"/>
+      <c r="A20" s="539"/>
+      <c r="B20" s="539"/>
       <c r="C20" s="279"/>
       <c r="D20" s="268"/>
       <c r="E20" s="268"/>
@@ -32572,12 +32593,12 @@
         <f ca="1">IF(Q20="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q20/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q20))</f>
         <v/>
       </c>
-      <c r="S20" s="535"/>
-      <c r="T20" s="537"/>
-      <c r="U20" s="539"/>
-      <c r="V20" s="541"/>
-      <c r="W20" s="529"/>
-      <c r="X20" s="531"/>
+      <c r="S20" s="541"/>
+      <c r="T20" s="543"/>
+      <c r="U20" s="553"/>
+      <c r="V20" s="555"/>
+      <c r="W20" s="557"/>
+      <c r="X20" s="559"/>
       <c r="Y20" s="274" t="str">
         <f>IF(B19="","",ROUNDUP(AVERAGE(R20,R20,X19),2))</f>
         <v/>
@@ -32588,10 +32609,10 @@
       </c>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="532">
+      <c r="A21" s="538">
         <v>6</v>
       </c>
-      <c r="B21" s="532" t="str">
+      <c r="B21" s="538" t="str">
         <f>IF('1. Halbjahr'!B9&lt;&gt;"", '1. Halbjahr'!B9, "")</f>
         <v/>
       </c>
@@ -32623,18 +32644,18 @@
         <f ca="1">IF(Q21="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q21/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q21))</f>
         <v/>
       </c>
-      <c r="S21" s="534"/>
-      <c r="T21" s="536"/>
-      <c r="U21" s="538"/>
-      <c r="V21" s="540" t="str">
+      <c r="S21" s="540"/>
+      <c r="T21" s="542"/>
+      <c r="U21" s="552"/>
+      <c r="V21" s="554" t="str">
         <f>IF(B21="","",SUM(S21:U21))</f>
         <v/>
       </c>
-      <c r="W21" s="528" t="str">
+      <c r="W21" s="556" t="str">
         <f>IF(B21="","",IF(ISBLANK(S21),"",IF(AVERAGE(S21:U21)&lt;10,LEFT(AVERAGE(S21:U21),4),LEFT(AVERAGE(S21:U21),5))))</f>
         <v/>
       </c>
-      <c r="X21" s="530" t="str">
+      <c r="X21" s="558" t="str">
         <f>IF(B21="","",IF(W21="","",IF(LEFT(W21,1)="0",0,ROUND(W21,0))))</f>
         <v/>
       </c>
@@ -32648,8 +32669,8 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="533"/>
-      <c r="B22" s="533"/>
+      <c r="A22" s="539"/>
+      <c r="B22" s="539"/>
       <c r="C22" s="279"/>
       <c r="D22" s="268"/>
       <c r="E22" s="268"/>
@@ -32678,12 +32699,12 @@
         <f ca="1">IF(Q22="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q22/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q22))</f>
         <v/>
       </c>
-      <c r="S22" s="535"/>
-      <c r="T22" s="537"/>
-      <c r="U22" s="539"/>
-      <c r="V22" s="541"/>
-      <c r="W22" s="529"/>
-      <c r="X22" s="531"/>
+      <c r="S22" s="541"/>
+      <c r="T22" s="543"/>
+      <c r="U22" s="553"/>
+      <c r="V22" s="555"/>
+      <c r="W22" s="557"/>
+      <c r="X22" s="559"/>
       <c r="Y22" s="274" t="str">
         <f>IF(B21="","",ROUNDUP(AVERAGE(R22,R22,X21),2))</f>
         <v/>
@@ -32694,10 +32715,10 @@
       </c>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="532">
+      <c r="A23" s="538">
         <v>7</v>
       </c>
-      <c r="B23" s="532" t="str">
+      <c r="B23" s="538" t="str">
         <f>IF('1. Halbjahr'!B10&lt;&gt;"", '1. Halbjahr'!B10, "")</f>
         <v/>
       </c>
@@ -32729,18 +32750,18 @@
         <f ca="1">IF(Q23="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q23/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q23))</f>
         <v/>
       </c>
-      <c r="S23" s="534"/>
-      <c r="T23" s="536"/>
-      <c r="U23" s="538"/>
-      <c r="V23" s="540" t="str">
+      <c r="S23" s="540"/>
+      <c r="T23" s="542"/>
+      <c r="U23" s="552"/>
+      <c r="V23" s="554" t="str">
         <f>IF(B23="","",SUM(S23:U23))</f>
         <v/>
       </c>
-      <c r="W23" s="528" t="str">
+      <c r="W23" s="556" t="str">
         <f>IF(B23="","",IF(ISBLANK(S23),"",IF(AVERAGE(S23:U23)&lt;10,LEFT(AVERAGE(S23:U23),4),LEFT(AVERAGE(S23:U23),5))))</f>
         <v/>
       </c>
-      <c r="X23" s="530" t="str">
+      <c r="X23" s="558" t="str">
         <f>IF(B23="","",IF(W23="","",IF(LEFT(W23,1)="0",0,ROUND(W23,0))))</f>
         <v/>
       </c>
@@ -32754,8 +32775,8 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="533"/>
-      <c r="B24" s="533"/>
+      <c r="A24" s="539"/>
+      <c r="B24" s="539"/>
       <c r="C24" s="279"/>
       <c r="D24" s="268"/>
       <c r="E24" s="268"/>
@@ -32784,12 +32805,12 @@
         <f ca="1">IF(Q24="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q24/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q24))</f>
         <v/>
       </c>
-      <c r="S24" s="535"/>
-      <c r="T24" s="537"/>
-      <c r="U24" s="539"/>
-      <c r="V24" s="541"/>
-      <c r="W24" s="529"/>
-      <c r="X24" s="531"/>
+      <c r="S24" s="541"/>
+      <c r="T24" s="543"/>
+      <c r="U24" s="553"/>
+      <c r="V24" s="555"/>
+      <c r="W24" s="557"/>
+      <c r="X24" s="559"/>
       <c r="Y24" s="274" t="str">
         <f>IF(B23="","",ROUNDUP(AVERAGE(R24,R24,X23),2))</f>
         <v/>
@@ -32800,10 +32821,10 @@
       </c>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="532">
+      <c r="A25" s="538">
         <v>8</v>
       </c>
-      <c r="B25" s="532" t="str">
+      <c r="B25" s="538" t="str">
         <f>IF('1. Halbjahr'!B11&lt;&gt;"", '1. Halbjahr'!B11, "")</f>
         <v/>
       </c>
@@ -32835,18 +32856,18 @@
         <f ca="1">IF(Q25="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q25/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q25))</f>
         <v/>
       </c>
-      <c r="S25" s="534"/>
-      <c r="T25" s="536"/>
-      <c r="U25" s="538"/>
-      <c r="V25" s="540" t="str">
+      <c r="S25" s="540"/>
+      <c r="T25" s="542"/>
+      <c r="U25" s="552"/>
+      <c r="V25" s="554" t="str">
         <f>IF(B25="","",SUM(S25:U25))</f>
         <v/>
       </c>
-      <c r="W25" s="528" t="str">
+      <c r="W25" s="556" t="str">
         <f>IF(B25="","",IF(ISBLANK(S25),"",IF(AVERAGE(S25:U25)&lt;10,LEFT(AVERAGE(S25:U25),4),LEFT(AVERAGE(S25:U25),5))))</f>
         <v/>
       </c>
-      <c r="X25" s="530" t="str">
+      <c r="X25" s="558" t="str">
         <f>IF(B25="","",IF(W25="","",IF(LEFT(W25,1)="0",0,ROUND(W25,0))))</f>
         <v/>
       </c>
@@ -32860,8 +32881,8 @@
       </c>
     </row>
     <row r="26" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="533"/>
-      <c r="B26" s="533"/>
+      <c r="A26" s="539"/>
+      <c r="B26" s="539"/>
       <c r="C26" s="279"/>
       <c r="D26" s="268"/>
       <c r="E26" s="268"/>
@@ -32890,12 +32911,12 @@
         <f ca="1">IF(Q26="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q26/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q26))</f>
         <v/>
       </c>
-      <c r="S26" s="535"/>
-      <c r="T26" s="537"/>
-      <c r="U26" s="539"/>
-      <c r="V26" s="541"/>
-      <c r="W26" s="529"/>
-      <c r="X26" s="531"/>
+      <c r="S26" s="541"/>
+      <c r="T26" s="543"/>
+      <c r="U26" s="553"/>
+      <c r="V26" s="555"/>
+      <c r="W26" s="557"/>
+      <c r="X26" s="559"/>
       <c r="Y26" s="274" t="str">
         <f>IF(B25="","",ROUNDUP(AVERAGE(R26,R26,X25),2))</f>
         <v/>
@@ -32906,10 +32927,10 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="532">
+      <c r="A27" s="538">
         <v>9</v>
       </c>
-      <c r="B27" s="532" t="str">
+      <c r="B27" s="538" t="str">
         <f>IF('1. Halbjahr'!B12&lt;&gt;"", '1. Halbjahr'!B12, "")</f>
         <v/>
       </c>
@@ -32941,18 +32962,18 @@
         <f ca="1">IF(Q27="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q27/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q27))</f>
         <v/>
       </c>
-      <c r="S27" s="534"/>
-      <c r="T27" s="536"/>
-      <c r="U27" s="538"/>
-      <c r="V27" s="540" t="str">
+      <c r="S27" s="540"/>
+      <c r="T27" s="542"/>
+      <c r="U27" s="552"/>
+      <c r="V27" s="554" t="str">
         <f>IF(B27="","",SUM(S27:U27))</f>
         <v/>
       </c>
-      <c r="W27" s="528" t="str">
+      <c r="W27" s="556" t="str">
         <f>IF(B27="","",IF(ISBLANK(S27),"",IF(AVERAGE(S27:U27)&lt;10,LEFT(AVERAGE(S27:U27),4),LEFT(AVERAGE(S27:U27),5))))</f>
         <v/>
       </c>
-      <c r="X27" s="530" t="str">
+      <c r="X27" s="558" t="str">
         <f>IF(B27="","",IF(W27="","",IF(LEFT(W27,1)="0",0,ROUND(W27,0))))</f>
         <v/>
       </c>
@@ -32966,8 +32987,8 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="533"/>
-      <c r="B28" s="533"/>
+      <c r="A28" s="539"/>
+      <c r="B28" s="539"/>
       <c r="C28" s="279"/>
       <c r="D28" s="268"/>
       <c r="E28" s="268"/>
@@ -32996,12 +33017,12 @@
         <f ca="1">IF(Q28="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q28/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q28))</f>
         <v/>
       </c>
-      <c r="S28" s="535"/>
-      <c r="T28" s="537"/>
-      <c r="U28" s="539"/>
-      <c r="V28" s="541"/>
-      <c r="W28" s="529"/>
-      <c r="X28" s="531"/>
+      <c r="S28" s="541"/>
+      <c r="T28" s="543"/>
+      <c r="U28" s="553"/>
+      <c r="V28" s="555"/>
+      <c r="W28" s="557"/>
+      <c r="X28" s="559"/>
       <c r="Y28" s="274" t="str">
         <f>IF(B27="","",ROUNDUP(AVERAGE(R28,R28,X27),2))</f>
         <v/>
@@ -33012,10 +33033,10 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="532">
+      <c r="A29" s="538">
         <v>10</v>
       </c>
-      <c r="B29" s="532" t="str">
+      <c r="B29" s="538" t="str">
         <f>IF('1. Halbjahr'!B13&lt;&gt;"", '1. Halbjahr'!B13, "")</f>
         <v/>
       </c>
@@ -33047,18 +33068,18 @@
         <f ca="1">IF(Q29="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q29/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q29))</f>
         <v/>
       </c>
-      <c r="S29" s="534"/>
-      <c r="T29" s="536"/>
-      <c r="U29" s="538"/>
-      <c r="V29" s="540" t="str">
+      <c r="S29" s="540"/>
+      <c r="T29" s="542"/>
+      <c r="U29" s="552"/>
+      <c r="V29" s="554" t="str">
         <f>IF(B29="","",SUM(S29:U29))</f>
         <v/>
       </c>
-      <c r="W29" s="528" t="str">
+      <c r="W29" s="556" t="str">
         <f>IF(B29="","",IF(ISBLANK(S29),"",IF(AVERAGE(S29:U29)&lt;10,LEFT(AVERAGE(S29:U29),4),LEFT(AVERAGE(S29:U29),5))))</f>
         <v/>
       </c>
-      <c r="X29" s="530" t="str">
+      <c r="X29" s="558" t="str">
         <f>IF(B29="","",IF(W29="","",IF(LEFT(W29,1)="0",0,ROUND(W29,0))))</f>
         <v/>
       </c>
@@ -33072,8 +33093,8 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="533"/>
-      <c r="B30" s="533"/>
+      <c r="A30" s="539"/>
+      <c r="B30" s="539"/>
       <c r="C30" s="279"/>
       <c r="D30" s="268"/>
       <c r="E30" s="268"/>
@@ -33102,12 +33123,12 @@
         <f ca="1">IF(Q30="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q30/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q30))</f>
         <v/>
       </c>
-      <c r="S30" s="535"/>
-      <c r="T30" s="537"/>
-      <c r="U30" s="539"/>
-      <c r="V30" s="541"/>
-      <c r="W30" s="529"/>
-      <c r="X30" s="531"/>
+      <c r="S30" s="541"/>
+      <c r="T30" s="543"/>
+      <c r="U30" s="553"/>
+      <c r="V30" s="555"/>
+      <c r="W30" s="557"/>
+      <c r="X30" s="559"/>
       <c r="Y30" s="274" t="str">
         <f>IF(B29="","",ROUNDUP(AVERAGE(R30,R30,X29),2))</f>
         <v/>
@@ -33118,10 +33139,10 @@
       </c>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="532">
+      <c r="A31" s="538">
         <v>11</v>
       </c>
-      <c r="B31" s="532" t="str">
+      <c r="B31" s="538" t="str">
         <f>IF('1. Halbjahr'!B14&lt;&gt;"", '1. Halbjahr'!B14, "")</f>
         <v/>
       </c>
@@ -33153,18 +33174,18 @@
         <f ca="1">IF(Q31="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q31/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q31))</f>
         <v/>
       </c>
-      <c r="S31" s="534"/>
-      <c r="T31" s="536"/>
-      <c r="U31" s="538"/>
-      <c r="V31" s="540" t="str">
+      <c r="S31" s="540"/>
+      <c r="T31" s="542"/>
+      <c r="U31" s="552"/>
+      <c r="V31" s="554" t="str">
         <f>IF(B31="","",SUM(S31:U31))</f>
         <v/>
       </c>
-      <c r="W31" s="528" t="str">
+      <c r="W31" s="556" t="str">
         <f>IF(B31="","",IF(ISBLANK(S31),"",IF(AVERAGE(S31:U31)&lt;10,LEFT(AVERAGE(S31:U31),4),LEFT(AVERAGE(S31:U31),5))))</f>
         <v/>
       </c>
-      <c r="X31" s="530" t="str">
+      <c r="X31" s="558" t="str">
         <f>IF(B31="","",IF(W31="","",IF(LEFT(W31,1)="0",0,ROUND(W31,0))))</f>
         <v/>
       </c>
@@ -33178,8 +33199,8 @@
       </c>
     </row>
     <row r="32" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="533"/>
-      <c r="B32" s="533"/>
+      <c r="A32" s="539"/>
+      <c r="B32" s="539"/>
       <c r="C32" s="279"/>
       <c r="D32" s="268"/>
       <c r="E32" s="268"/>
@@ -33208,12 +33229,12 @@
         <f ca="1">IF(Q32="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q32/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q32))</f>
         <v/>
       </c>
-      <c r="S32" s="535"/>
-      <c r="T32" s="537"/>
-      <c r="U32" s="539"/>
-      <c r="V32" s="541"/>
-      <c r="W32" s="529"/>
-      <c r="X32" s="531"/>
+      <c r="S32" s="541"/>
+      <c r="T32" s="543"/>
+      <c r="U32" s="553"/>
+      <c r="V32" s="555"/>
+      <c r="W32" s="557"/>
+      <c r="X32" s="559"/>
       <c r="Y32" s="274" t="str">
         <f>IF(B31="","",ROUNDUP(AVERAGE(R32,R32,X31),2))</f>
         <v/>
@@ -33224,10 +33245,10 @@
       </c>
     </row>
     <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="532">
+      <c r="A33" s="538">
         <v>12</v>
       </c>
-      <c r="B33" s="532" t="str">
+      <c r="B33" s="538" t="str">
         <f>IF('1. Halbjahr'!B15&lt;&gt;"", '1. Halbjahr'!B15, "")</f>
         <v/>
       </c>
@@ -33259,18 +33280,18 @@
         <f ca="1">IF(Q33="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q33/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q33))</f>
         <v/>
       </c>
-      <c r="S33" s="534"/>
-      <c r="T33" s="536"/>
-      <c r="U33" s="538"/>
-      <c r="V33" s="540" t="str">
+      <c r="S33" s="540"/>
+      <c r="T33" s="542"/>
+      <c r="U33" s="552"/>
+      <c r="V33" s="554" t="str">
         <f>IF(B33="","",SUM(S33:U33))</f>
         <v/>
       </c>
-      <c r="W33" s="528" t="str">
+      <c r="W33" s="556" t="str">
         <f>IF(B33="","",IF(ISBLANK(S33),"",IF(AVERAGE(S33:U33)&lt;10,LEFT(AVERAGE(S33:U33),4),LEFT(AVERAGE(S33:U33),5))))</f>
         <v/>
       </c>
-      <c r="X33" s="530" t="str">
+      <c r="X33" s="558" t="str">
         <f>IF(B33="","",IF(W33="","",IF(LEFT(W33,1)="0",0,ROUND(W33,0))))</f>
         <v/>
       </c>
@@ -33284,8 +33305,8 @@
       </c>
     </row>
     <row r="34" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="533"/>
-      <c r="B34" s="533"/>
+      <c r="A34" s="539"/>
+      <c r="B34" s="539"/>
       <c r="C34" s="279"/>
       <c r="D34" s="268"/>
       <c r="E34" s="268"/>
@@ -33314,12 +33335,12 @@
         <f ca="1">IF(Q34="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q34/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q34))</f>
         <v/>
       </c>
-      <c r="S34" s="535"/>
-      <c r="T34" s="537"/>
-      <c r="U34" s="539"/>
-      <c r="V34" s="541"/>
-      <c r="W34" s="529"/>
-      <c r="X34" s="531"/>
+      <c r="S34" s="541"/>
+      <c r="T34" s="543"/>
+      <c r="U34" s="553"/>
+      <c r="V34" s="555"/>
+      <c r="W34" s="557"/>
+      <c r="X34" s="559"/>
       <c r="Y34" s="274" t="str">
         <f>IF(B33="","",ROUNDUP(AVERAGE(R34,R34,X33),2))</f>
         <v/>
@@ -33330,10 +33351,10 @@
       </c>
     </row>
     <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="532">
+      <c r="A35" s="538">
         <v>13</v>
       </c>
-      <c r="B35" s="532" t="str">
+      <c r="B35" s="538" t="str">
         <f>IF('1. Halbjahr'!B16&lt;&gt;"", '1. Halbjahr'!B16, "")</f>
         <v/>
       </c>
@@ -33365,18 +33386,18 @@
         <f ca="1">IF(Q35="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q35/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q35))</f>
         <v/>
       </c>
-      <c r="S35" s="534"/>
-      <c r="T35" s="536"/>
-      <c r="U35" s="538"/>
-      <c r="V35" s="540" t="str">
+      <c r="S35" s="540"/>
+      <c r="T35" s="542"/>
+      <c r="U35" s="552"/>
+      <c r="V35" s="554" t="str">
         <f>IF(B35="","",SUM(S35:U35))</f>
         <v/>
       </c>
-      <c r="W35" s="528" t="str">
+      <c r="W35" s="556" t="str">
         <f>IF(B35="","",IF(ISBLANK(S35),"",IF(AVERAGE(S35:U35)&lt;10,LEFT(AVERAGE(S35:U35),4),LEFT(AVERAGE(S35:U35),5))))</f>
         <v/>
       </c>
-      <c r="X35" s="530" t="str">
+      <c r="X35" s="558" t="str">
         <f>IF(B35="","",IF(W35="","",IF(LEFT(W35,1)="0",0,ROUND(W35,0))))</f>
         <v/>
       </c>
@@ -33390,8 +33411,8 @@
       </c>
     </row>
     <row r="36" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="533"/>
-      <c r="B36" s="533"/>
+      <c r="A36" s="539"/>
+      <c r="B36" s="539"/>
       <c r="C36" s="279"/>
       <c r="D36" s="268"/>
       <c r="E36" s="268"/>
@@ -33420,12 +33441,12 @@
         <f ca="1">IF(Q36="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q36/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q36))</f>
         <v/>
       </c>
-      <c r="S36" s="535"/>
-      <c r="T36" s="537"/>
-      <c r="U36" s="539"/>
-      <c r="V36" s="541"/>
-      <c r="W36" s="529"/>
-      <c r="X36" s="531"/>
+      <c r="S36" s="541"/>
+      <c r="T36" s="543"/>
+      <c r="U36" s="553"/>
+      <c r="V36" s="555"/>
+      <c r="W36" s="557"/>
+      <c r="X36" s="559"/>
       <c r="Y36" s="274" t="str">
         <f>IF(B35="","",ROUNDUP(AVERAGE(R36,R36,X35),2))</f>
         <v/>
@@ -33436,10 +33457,10 @@
       </c>
     </row>
     <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="532">
+      <c r="A37" s="538">
         <v>14</v>
       </c>
-      <c r="B37" s="532" t="str">
+      <c r="B37" s="538" t="str">
         <f>IF('1. Halbjahr'!B17&lt;&gt;"", '1. Halbjahr'!B17, "")</f>
         <v/>
       </c>
@@ -33471,18 +33492,18 @@
         <f ca="1">IF(Q37="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q37/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q37))</f>
         <v/>
       </c>
-      <c r="S37" s="534"/>
-      <c r="T37" s="536"/>
-      <c r="U37" s="538"/>
-      <c r="V37" s="540" t="str">
+      <c r="S37" s="540"/>
+      <c r="T37" s="542"/>
+      <c r="U37" s="552"/>
+      <c r="V37" s="554" t="str">
         <f>IF(B37="","",SUM(S37:U37))</f>
         <v/>
       </c>
-      <c r="W37" s="528" t="str">
+      <c r="W37" s="556" t="str">
         <f>IF(B37="","",IF(ISBLANK(S37),"",IF(AVERAGE(S37:U37)&lt;10,LEFT(AVERAGE(S37:U37),4),LEFT(AVERAGE(S37:U37),5))))</f>
         <v/>
       </c>
-      <c r="X37" s="530" t="str">
+      <c r="X37" s="558" t="str">
         <f>IF(B37="","",IF(W37="","",IF(LEFT(W37,1)="0",0,ROUND(W37,0))))</f>
         <v/>
       </c>
@@ -33496,8 +33517,8 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="533"/>
-      <c r="B38" s="533"/>
+      <c r="A38" s="539"/>
+      <c r="B38" s="539"/>
       <c r="C38" s="279"/>
       <c r="D38" s="268"/>
       <c r="E38" s="268"/>
@@ -33526,12 +33547,12 @@
         <f ca="1">IF(Q38="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q38/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q38))</f>
         <v/>
       </c>
-      <c r="S38" s="535"/>
-      <c r="T38" s="537"/>
-      <c r="U38" s="539"/>
-      <c r="V38" s="541"/>
-      <c r="W38" s="529"/>
-      <c r="X38" s="531"/>
+      <c r="S38" s="541"/>
+      <c r="T38" s="543"/>
+      <c r="U38" s="553"/>
+      <c r="V38" s="555"/>
+      <c r="W38" s="557"/>
+      <c r="X38" s="559"/>
       <c r="Y38" s="274" t="str">
         <f>IF(B37="","",ROUNDUP(AVERAGE(R38,R38,X37),2))</f>
         <v/>
@@ -33542,10 +33563,10 @@
       </c>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="532">
+      <c r="A39" s="538">
         <v>15</v>
       </c>
-      <c r="B39" s="532" t="str">
+      <c r="B39" s="538" t="str">
         <f>IF('1. Halbjahr'!B18&lt;&gt;"", '1. Halbjahr'!B18, "")</f>
         <v/>
       </c>
@@ -33577,18 +33598,18 @@
         <f ca="1">IF(Q39="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q39/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q39))</f>
         <v/>
       </c>
-      <c r="S39" s="542"/>
-      <c r="T39" s="543"/>
-      <c r="U39" s="544"/>
-      <c r="V39" s="545" t="str">
+      <c r="S39" s="560"/>
+      <c r="T39" s="561"/>
+      <c r="U39" s="562"/>
+      <c r="V39" s="563" t="str">
         <f>IF(B39="","",SUM(S39:U39))</f>
         <v/>
       </c>
-      <c r="W39" s="528" t="str">
+      <c r="W39" s="556" t="str">
         <f>IF(B39="","",IF(ISBLANK(S39),"",IF(AVERAGE(S39:U39)&lt;10,LEFT(AVERAGE(S39:U39),4),LEFT(AVERAGE(S39:U39),5))))</f>
         <v/>
       </c>
-      <c r="X39" s="530" t="str">
+      <c r="X39" s="558" t="str">
         <f>IF(B39="","",IF(W39="","",IF(LEFT(W39,1)="0",0,ROUND(W39,0))))</f>
         <v/>
       </c>
@@ -33602,8 +33623,8 @@
       </c>
     </row>
     <row r="40" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="533"/>
-      <c r="B40" s="533"/>
+      <c r="A40" s="539"/>
+      <c r="B40" s="539"/>
       <c r="C40" s="279"/>
       <c r="D40" s="268"/>
       <c r="E40" s="268"/>
@@ -33632,12 +33653,12 @@
         <f ca="1">IF(Q40="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q40/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q40))</f>
         <v/>
       </c>
-      <c r="S40" s="535"/>
-      <c r="T40" s="537"/>
-      <c r="U40" s="539"/>
-      <c r="V40" s="541"/>
-      <c r="W40" s="529"/>
-      <c r="X40" s="531"/>
+      <c r="S40" s="541"/>
+      <c r="T40" s="543"/>
+      <c r="U40" s="553"/>
+      <c r="V40" s="555"/>
+      <c r="W40" s="557"/>
+      <c r="X40" s="559"/>
       <c r="Y40" s="274" t="str">
         <f>IF(B39="","",ROUNDUP(AVERAGE(R40,R40,X39),2))</f>
         <v/>
@@ -33648,10 +33669,10 @@
       </c>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="532">
+      <c r="A41" s="538">
         <v>16</v>
       </c>
-      <c r="B41" s="532" t="str">
+      <c r="B41" s="538" t="str">
         <f>IF('1. Halbjahr'!B19&lt;&gt;"", '1. Halbjahr'!B19, "")</f>
         <v/>
       </c>
@@ -33683,18 +33704,18 @@
         <f ca="1">IF(Q41="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q41/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q41))</f>
         <v/>
       </c>
-      <c r="S41" s="534"/>
-      <c r="T41" s="536"/>
-      <c r="U41" s="538"/>
-      <c r="V41" s="540" t="str">
+      <c r="S41" s="540"/>
+      <c r="T41" s="542"/>
+      <c r="U41" s="552"/>
+      <c r="V41" s="554" t="str">
         <f>IF(B41="","",SUM(S41:U41))</f>
         <v/>
       </c>
-      <c r="W41" s="528" t="str">
+      <c r="W41" s="556" t="str">
         <f>IF(B41="","",IF(ISBLANK(S41),"",IF(AVERAGE(S41:U41)&lt;10,LEFT(AVERAGE(S41:U41),4),LEFT(AVERAGE(S41:U41),5))))</f>
         <v/>
       </c>
-      <c r="X41" s="530" t="str">
+      <c r="X41" s="558" t="str">
         <f>IF(B41="","",IF(W41="","",IF(LEFT(W41,1)="0",0,ROUND(W41,0))))</f>
         <v/>
       </c>
@@ -33708,8 +33729,8 @@
       </c>
     </row>
     <row r="42" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="533"/>
-      <c r="B42" s="533"/>
+      <c r="A42" s="539"/>
+      <c r="B42" s="539"/>
       <c r="C42" s="279"/>
       <c r="D42" s="268"/>
       <c r="E42" s="268"/>
@@ -33738,12 +33759,12 @@
         <f ca="1">IF(Q42="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q42/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q42))</f>
         <v/>
       </c>
-      <c r="S42" s="535"/>
-      <c r="T42" s="537"/>
-      <c r="U42" s="539"/>
-      <c r="V42" s="541"/>
-      <c r="W42" s="529"/>
-      <c r="X42" s="531"/>
+      <c r="S42" s="541"/>
+      <c r="T42" s="543"/>
+      <c r="U42" s="553"/>
+      <c r="V42" s="555"/>
+      <c r="W42" s="557"/>
+      <c r="X42" s="559"/>
       <c r="Y42" s="274" t="str">
         <f>IF(B41="","",ROUNDUP(AVERAGE(R42,R42,X41),2))</f>
         <v/>
@@ -33754,10 +33775,10 @@
       </c>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="532">
+      <c r="A43" s="538">
         <v>17</v>
       </c>
-      <c r="B43" s="532" t="str">
+      <c r="B43" s="538" t="str">
         <f>IF('1. Halbjahr'!B20&lt;&gt;"", '1. Halbjahr'!B20, "")</f>
         <v/>
       </c>
@@ -33789,18 +33810,18 @@
         <f ca="1">IF(Q43="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q43/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q43))</f>
         <v/>
       </c>
-      <c r="S43" s="534"/>
-      <c r="T43" s="536"/>
-      <c r="U43" s="538"/>
-      <c r="V43" s="540" t="str">
+      <c r="S43" s="540"/>
+      <c r="T43" s="542"/>
+      <c r="U43" s="552"/>
+      <c r="V43" s="554" t="str">
         <f>IF(B43="","",SUM(S43:U43))</f>
         <v/>
       </c>
-      <c r="W43" s="528" t="str">
+      <c r="W43" s="556" t="str">
         <f>IF(B43="","",IF(ISBLANK(S43),"",IF(AVERAGE(S43:U43)&lt;10,LEFT(AVERAGE(S43:U43),4),LEFT(AVERAGE(S43:U43),5))))</f>
         <v/>
       </c>
-      <c r="X43" s="530" t="str">
+      <c r="X43" s="558" t="str">
         <f>IF(B43="","",IF(W43="","",IF(LEFT(W43,1)="0",0,ROUND(W43,0))))</f>
         <v/>
       </c>
@@ -33814,8 +33835,8 @@
       </c>
     </row>
     <row r="44" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="533"/>
-      <c r="B44" s="533"/>
+      <c r="A44" s="539"/>
+      <c r="B44" s="539"/>
       <c r="C44" s="279"/>
       <c r="D44" s="268"/>
       <c r="E44" s="268"/>
@@ -33844,12 +33865,12 @@
         <f ca="1">IF(Q44="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q44/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q44))</f>
         <v/>
       </c>
-      <c r="S44" s="535"/>
-      <c r="T44" s="537"/>
-      <c r="U44" s="539"/>
-      <c r="V44" s="541"/>
-      <c r="W44" s="529"/>
-      <c r="X44" s="531"/>
+      <c r="S44" s="541"/>
+      <c r="T44" s="543"/>
+      <c r="U44" s="553"/>
+      <c r="V44" s="555"/>
+      <c r="W44" s="557"/>
+      <c r="X44" s="559"/>
       <c r="Y44" s="274" t="str">
         <f>IF(B43="","",ROUNDUP(AVERAGE(R44,R44,X43),2))</f>
         <v/>
@@ -33860,10 +33881,10 @@
       </c>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="532">
+      <c r="A45" s="538">
         <v>18</v>
       </c>
-      <c r="B45" s="532" t="str">
+      <c r="B45" s="538" t="str">
         <f>IF('1. Halbjahr'!B21&lt;&gt;"", '1. Halbjahr'!B21, "")</f>
         <v/>
       </c>
@@ -33895,18 +33916,18 @@
         <f ca="1">IF(Q45="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q45/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q45))</f>
         <v/>
       </c>
-      <c r="S45" s="534"/>
-      <c r="T45" s="536"/>
-      <c r="U45" s="538"/>
-      <c r="V45" s="540" t="str">
+      <c r="S45" s="540"/>
+      <c r="T45" s="542"/>
+      <c r="U45" s="552"/>
+      <c r="V45" s="554" t="str">
         <f>IF(B45="","",SUM(S45:U45))</f>
         <v/>
       </c>
-      <c r="W45" s="528" t="str">
+      <c r="W45" s="556" t="str">
         <f>IF(B45="","",IF(ISBLANK(S45),"",IF(AVERAGE(S45:U45)&lt;10,LEFT(AVERAGE(S45:U45),4),LEFT(AVERAGE(S45:U45),5))))</f>
         <v/>
       </c>
-      <c r="X45" s="530" t="str">
+      <c r="X45" s="558" t="str">
         <f>IF(B45="","",IF(W45="","",IF(LEFT(W45,1)="0",0,ROUND(W45,0))))</f>
         <v/>
       </c>
@@ -33920,8 +33941,8 @@
       </c>
     </row>
     <row r="46" spans="1:26" s="217" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="533"/>
-      <c r="B46" s="533"/>
+      <c r="A46" s="539"/>
+      <c r="B46" s="539"/>
       <c r="C46" s="284"/>
       <c r="D46" s="285"/>
       <c r="E46" s="285"/>
@@ -33950,12 +33971,12 @@
         <f ca="1">IF(Q46="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q46/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q46))</f>
         <v/>
       </c>
-      <c r="S46" s="535"/>
-      <c r="T46" s="537"/>
-      <c r="U46" s="539"/>
-      <c r="V46" s="541"/>
-      <c r="W46" s="529"/>
-      <c r="X46" s="531"/>
+      <c r="S46" s="541"/>
+      <c r="T46" s="543"/>
+      <c r="U46" s="553"/>
+      <c r="V46" s="555"/>
+      <c r="W46" s="557"/>
+      <c r="X46" s="559"/>
       <c r="Y46" s="274" t="str">
         <f>IF(B45="","",ROUNDUP(AVERAGE(R46,R46,X45),2))</f>
         <v/>
@@ -33966,10 +33987,10 @@
       </c>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="532">
+      <c r="A47" s="538">
         <v>19</v>
       </c>
-      <c r="B47" s="532" t="str">
+      <c r="B47" s="538" t="str">
         <f>IF('1. Halbjahr'!B22&lt;&gt;"", '1. Halbjahr'!B22, "")</f>
         <v/>
       </c>
@@ -34001,18 +34022,18 @@
         <f ca="1">IF(Q47="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q47/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q47))</f>
         <v/>
       </c>
-      <c r="S47" s="534"/>
-      <c r="T47" s="536"/>
-      <c r="U47" s="538"/>
-      <c r="V47" s="540" t="str">
+      <c r="S47" s="540"/>
+      <c r="T47" s="542"/>
+      <c r="U47" s="552"/>
+      <c r="V47" s="554" t="str">
         <f>IF(B47="","",SUM(S47:U47))</f>
         <v/>
       </c>
-      <c r="W47" s="528" t="str">
+      <c r="W47" s="556" t="str">
         <f>IF(B47="","",IF(ISBLANK(S47),"",IF(AVERAGE(S47:U47)&lt;10,LEFT(AVERAGE(S47:U47),4),LEFT(AVERAGE(S47:U47),5))))</f>
         <v/>
       </c>
-      <c r="X47" s="530" t="str">
+      <c r="X47" s="558" t="str">
         <f>IF(B47="","",IF(W47="","",IF(LEFT(W47,1)="0",0,ROUND(W47,0))))</f>
         <v/>
       </c>
@@ -34026,8 +34047,8 @@
       </c>
     </row>
     <row r="48" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="533"/>
-      <c r="B48" s="533"/>
+      <c r="A48" s="539"/>
+      <c r="B48" s="539"/>
       <c r="C48" s="279"/>
       <c r="D48" s="268"/>
       <c r="E48" s="268"/>
@@ -34056,12 +34077,12 @@
         <f ca="1">IF(Q48="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q48/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q48))</f>
         <v/>
       </c>
-      <c r="S48" s="535"/>
-      <c r="T48" s="537"/>
-      <c r="U48" s="539"/>
-      <c r="V48" s="541"/>
-      <c r="W48" s="529"/>
-      <c r="X48" s="531"/>
+      <c r="S48" s="541"/>
+      <c r="T48" s="543"/>
+      <c r="U48" s="553"/>
+      <c r="V48" s="555"/>
+      <c r="W48" s="557"/>
+      <c r="X48" s="559"/>
       <c r="Y48" s="274" t="str">
         <f>IF(B47="","",ROUNDUP(AVERAGE(R48,R48,X47),2))</f>
         <v/>
@@ -34072,10 +34093,10 @@
       </c>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="532">
+      <c r="A49" s="538">
         <v>20</v>
       </c>
-      <c r="B49" s="532" t="str">
+      <c r="B49" s="538" t="str">
         <f>IF('1. Halbjahr'!B23&lt;&gt;"", '1. Halbjahr'!B23, "")</f>
         <v/>
       </c>
@@ -34107,18 +34128,18 @@
         <f ca="1">IF(Q49="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q49/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q49))</f>
         <v/>
       </c>
-      <c r="S49" s="534"/>
-      <c r="T49" s="536"/>
-      <c r="U49" s="538"/>
-      <c r="V49" s="540" t="str">
+      <c r="S49" s="540"/>
+      <c r="T49" s="542"/>
+      <c r="U49" s="552"/>
+      <c r="V49" s="554" t="str">
         <f>IF(B49="","",SUM(S49:U49))</f>
         <v/>
       </c>
-      <c r="W49" s="528" t="str">
+      <c r="W49" s="556" t="str">
         <f>IF(B49="","",IF(ISBLANK(S49),"",IF(AVERAGE(S49:U49)&lt;10,LEFT(AVERAGE(S49:U49),4),LEFT(AVERAGE(S49:U49),5))))</f>
         <v/>
       </c>
-      <c r="X49" s="530" t="str">
+      <c r="X49" s="558" t="str">
         <f>IF(B49="","",IF(W49="","",IF(LEFT(W49,1)="0",0,ROUND(W49,0))))</f>
         <v/>
       </c>
@@ -34132,8 +34153,8 @@
       </c>
     </row>
     <row r="50" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="533"/>
-      <c r="B50" s="533"/>
+      <c r="A50" s="539"/>
+      <c r="B50" s="539"/>
       <c r="C50" s="279"/>
       <c r="D50" s="268"/>
       <c r="E50" s="268"/>
@@ -34162,12 +34183,12 @@
         <f ca="1">IF(Q50="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q50/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q50))</f>
         <v/>
       </c>
-      <c r="S50" s="535"/>
-      <c r="T50" s="537"/>
-      <c r="U50" s="539"/>
-      <c r="V50" s="541"/>
-      <c r="W50" s="529"/>
-      <c r="X50" s="531"/>
+      <c r="S50" s="541"/>
+      <c r="T50" s="543"/>
+      <c r="U50" s="553"/>
+      <c r="V50" s="555"/>
+      <c r="W50" s="557"/>
+      <c r="X50" s="559"/>
       <c r="Y50" s="274" t="str">
         <f>IF(B49="","",ROUNDUP(AVERAGE(R50,R50,X49),2))</f>
         <v/>
@@ -34178,10 +34199,10 @@
       </c>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="532">
+      <c r="A51" s="538">
         <v>21</v>
       </c>
-      <c r="B51" s="532" t="str">
+      <c r="B51" s="538" t="str">
         <f>IF('1. Halbjahr'!B24&lt;&gt;"", '1. Halbjahr'!B24, "")</f>
         <v/>
       </c>
@@ -34213,18 +34234,18 @@
         <f ca="1">IF(Q51="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q51/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q51))</f>
         <v/>
       </c>
-      <c r="S51" s="534"/>
-      <c r="T51" s="536"/>
-      <c r="U51" s="538"/>
-      <c r="V51" s="540" t="str">
+      <c r="S51" s="540"/>
+      <c r="T51" s="542"/>
+      <c r="U51" s="552"/>
+      <c r="V51" s="554" t="str">
         <f>IF(B51="","",SUM(S51:U51))</f>
         <v/>
       </c>
-      <c r="W51" s="528" t="str">
+      <c r="W51" s="556" t="str">
         <f>IF(B51="","",IF(ISBLANK(S51),"",IF(AVERAGE(S51:U51)&lt;10,LEFT(AVERAGE(S51:U51),4),LEFT(AVERAGE(S51:U51),5))))</f>
         <v/>
       </c>
-      <c r="X51" s="530" t="str">
+      <c r="X51" s="558" t="str">
         <f>IF(B51="","",IF(W51="","",IF(LEFT(W51,1)="0",0,ROUND(W51,0))))</f>
         <v/>
       </c>
@@ -34238,8 +34259,8 @@
       </c>
     </row>
     <row r="52" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="533"/>
-      <c r="B52" s="533"/>
+      <c r="A52" s="539"/>
+      <c r="B52" s="539"/>
       <c r="C52" s="279"/>
       <c r="D52" s="268"/>
       <c r="E52" s="268"/>
@@ -34268,12 +34289,12 @@
         <f ca="1">IF(Q52="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q52/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q52))</f>
         <v/>
       </c>
-      <c r="S52" s="535"/>
-      <c r="T52" s="537"/>
-      <c r="U52" s="539"/>
-      <c r="V52" s="541"/>
-      <c r="W52" s="529"/>
-      <c r="X52" s="531"/>
+      <c r="S52" s="541"/>
+      <c r="T52" s="543"/>
+      <c r="U52" s="553"/>
+      <c r="V52" s="555"/>
+      <c r="W52" s="557"/>
+      <c r="X52" s="559"/>
       <c r="Y52" s="274" t="str">
         <f>IF(B51="","",ROUNDUP(AVERAGE(R52,R52,X51),2))</f>
         <v/>
@@ -34284,10 +34305,10 @@
       </c>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="532">
+      <c r="A53" s="538">
         <v>22</v>
       </c>
-      <c r="B53" s="532" t="str">
+      <c r="B53" s="538" t="str">
         <f>IF('1. Halbjahr'!B25&lt;&gt;"", '1. Halbjahr'!B25, "")</f>
         <v/>
       </c>
@@ -34319,18 +34340,18 @@
         <f ca="1">IF(Q53="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q53/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q53))</f>
         <v/>
       </c>
-      <c r="S53" s="534"/>
-      <c r="T53" s="536"/>
-      <c r="U53" s="538"/>
-      <c r="V53" s="540" t="str">
+      <c r="S53" s="540"/>
+      <c r="T53" s="542"/>
+      <c r="U53" s="552"/>
+      <c r="V53" s="554" t="str">
         <f>IF(B53="","",SUM(S53:U53))</f>
         <v/>
       </c>
-      <c r="W53" s="528" t="str">
+      <c r="W53" s="556" t="str">
         <f>IF(B53="","",IF(ISBLANK(S53),"",IF(AVERAGE(S53:U53)&lt;10,LEFT(AVERAGE(S53:U53),4),LEFT(AVERAGE(S53:U53),5))))</f>
         <v/>
       </c>
-      <c r="X53" s="530" t="str">
+      <c r="X53" s="558" t="str">
         <f>IF(B53="","",IF(W53="","",IF(LEFT(W53,1)="0",0,ROUND(W53,0))))</f>
         <v/>
       </c>
@@ -34344,8 +34365,8 @@
       </c>
     </row>
     <row r="54" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="533"/>
-      <c r="B54" s="533"/>
+      <c r="A54" s="539"/>
+      <c r="B54" s="539"/>
       <c r="C54" s="279"/>
       <c r="D54" s="268"/>
       <c r="E54" s="268"/>
@@ -34374,12 +34395,12 @@
         <f ca="1">IF(Q54="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q54/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q54))</f>
         <v/>
       </c>
-      <c r="S54" s="535"/>
-      <c r="T54" s="537"/>
-      <c r="U54" s="539"/>
-      <c r="V54" s="541"/>
-      <c r="W54" s="529"/>
-      <c r="X54" s="531"/>
+      <c r="S54" s="541"/>
+      <c r="T54" s="543"/>
+      <c r="U54" s="553"/>
+      <c r="V54" s="555"/>
+      <c r="W54" s="557"/>
+      <c r="X54" s="559"/>
       <c r="Y54" s="274" t="str">
         <f>IF(B53="","",ROUNDUP(AVERAGE(R54,R54,X53),2))</f>
         <v/>
@@ -34390,10 +34411,10 @@
       </c>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="532">
+      <c r="A55" s="538">
         <v>23</v>
       </c>
-      <c r="B55" s="532" t="str">
+      <c r="B55" s="538" t="str">
         <f>IF('1. Halbjahr'!B26&lt;&gt;"", '1. Halbjahr'!B26, "")</f>
         <v/>
       </c>
@@ -34425,18 +34446,18 @@
         <f ca="1">IF(Q55="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q55/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q55))</f>
         <v/>
       </c>
-      <c r="S55" s="534"/>
-      <c r="T55" s="536"/>
-      <c r="U55" s="538"/>
-      <c r="V55" s="540" t="str">
+      <c r="S55" s="540"/>
+      <c r="T55" s="542"/>
+      <c r="U55" s="552"/>
+      <c r="V55" s="554" t="str">
         <f>IF(B55="","",SUM(S55:U55))</f>
         <v/>
       </c>
-      <c r="W55" s="528" t="str">
+      <c r="W55" s="556" t="str">
         <f>IF(B55="","",IF(ISBLANK(S55),"",IF(AVERAGE(S55:U55)&lt;10,LEFT(AVERAGE(S55:U55),4),LEFT(AVERAGE(S55:U55),5))))</f>
         <v/>
       </c>
-      <c r="X55" s="530" t="str">
+      <c r="X55" s="558" t="str">
         <f>IF(B55="","",IF(W55="","",IF(LEFT(W55,1)="0",0,ROUND(W55,0))))</f>
         <v/>
       </c>
@@ -34450,8 +34471,8 @@
       </c>
     </row>
     <row r="56" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="533"/>
-      <c r="B56" s="533"/>
+      <c r="A56" s="539"/>
+      <c r="B56" s="539"/>
       <c r="C56" s="279"/>
       <c r="D56" s="268"/>
       <c r="E56" s="268"/>
@@ -34480,12 +34501,12 @@
         <f ca="1">IF(Q56="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q56/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q56))</f>
         <v/>
       </c>
-      <c r="S56" s="535"/>
-      <c r="T56" s="537"/>
-      <c r="U56" s="539"/>
-      <c r="V56" s="541"/>
-      <c r="W56" s="529"/>
-      <c r="X56" s="531"/>
+      <c r="S56" s="541"/>
+      <c r="T56" s="543"/>
+      <c r="U56" s="553"/>
+      <c r="V56" s="555"/>
+      <c r="W56" s="557"/>
+      <c r="X56" s="559"/>
       <c r="Y56" s="274" t="str">
         <f>IF(B55="","",ROUNDUP(AVERAGE(R56,R56,X55),2))</f>
         <v/>
@@ -34496,10 +34517,10 @@
       </c>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="532">
+      <c r="A57" s="538">
         <v>24</v>
       </c>
-      <c r="B57" s="532" t="str">
+      <c r="B57" s="538" t="str">
         <f>IF('1. Halbjahr'!B27&lt;&gt;"", '1. Halbjahr'!B27, "")</f>
         <v/>
       </c>
@@ -34531,18 +34552,18 @@
         <f ca="1">IF(Q57="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q57/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q57))</f>
         <v/>
       </c>
-      <c r="S57" s="534"/>
-      <c r="T57" s="536"/>
-      <c r="U57" s="538"/>
-      <c r="V57" s="540" t="str">
+      <c r="S57" s="540"/>
+      <c r="T57" s="542"/>
+      <c r="U57" s="552"/>
+      <c r="V57" s="554" t="str">
         <f>IF(B57="","",SUM(S57:U57))</f>
         <v/>
       </c>
-      <c r="W57" s="528" t="str">
+      <c r="W57" s="556" t="str">
         <f>IF(B57="","",IF(ISBLANK(S57),"",IF(AVERAGE(S57:U57)&lt;10,LEFT(AVERAGE(S57:U57),4),LEFT(AVERAGE(S57:U57),5))))</f>
         <v/>
       </c>
-      <c r="X57" s="530" t="str">
+      <c r="X57" s="558" t="str">
         <f>IF(B57="","",IF(W57="","",IF(LEFT(W57,1)="0",0,ROUND(W57,0))))</f>
         <v/>
       </c>
@@ -34556,8 +34577,8 @@
       </c>
     </row>
     <row r="58" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="533"/>
-      <c r="B58" s="533"/>
+      <c r="A58" s="539"/>
+      <c r="B58" s="539"/>
       <c r="C58" s="279"/>
       <c r="D58" s="268"/>
       <c r="E58" s="268"/>
@@ -34586,12 +34607,12 @@
         <f ca="1">IF(Q58="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q58/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q58))</f>
         <v/>
       </c>
-      <c r="S58" s="535"/>
-      <c r="T58" s="537"/>
-      <c r="U58" s="539"/>
-      <c r="V58" s="541"/>
-      <c r="W58" s="529"/>
-      <c r="X58" s="531"/>
+      <c r="S58" s="541"/>
+      <c r="T58" s="543"/>
+      <c r="U58" s="553"/>
+      <c r="V58" s="555"/>
+      <c r="W58" s="557"/>
+      <c r="X58" s="559"/>
       <c r="Y58" s="274" t="str">
         <f>IF(B57="","",ROUNDUP(AVERAGE(R58,R58,X57),2))</f>
         <v/>
@@ -34602,10 +34623,10 @@
       </c>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="532">
+      <c r="A59" s="538">
         <v>25</v>
       </c>
-      <c r="B59" s="532" t="str">
+      <c r="B59" s="538" t="str">
         <f>IF('1. Halbjahr'!B28&lt;&gt;"", '1. Halbjahr'!B28, "")</f>
         <v/>
       </c>
@@ -34637,18 +34658,18 @@
         <f ca="1">IF(Q59="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q59/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q59))</f>
         <v/>
       </c>
-      <c r="S59" s="534"/>
-      <c r="T59" s="536"/>
-      <c r="U59" s="538"/>
-      <c r="V59" s="540" t="str">
+      <c r="S59" s="540"/>
+      <c r="T59" s="542"/>
+      <c r="U59" s="552"/>
+      <c r="V59" s="554" t="str">
         <f>IF(B59="","",SUM(S59:U59))</f>
         <v/>
       </c>
-      <c r="W59" s="528" t="str">
+      <c r="W59" s="556" t="str">
         <f>IF(B59="","",IF(ISBLANK(S59),"",IF(AVERAGE(S59:U59)&lt;10,LEFT(AVERAGE(S59:U59),4),LEFT(AVERAGE(S59:U59),5))))</f>
         <v/>
       </c>
-      <c r="X59" s="530" t="str">
+      <c r="X59" s="558" t="str">
         <f>IF(B59="","",IF(W59="","",IF(LEFT(W59,1)="0",0,ROUND(W59,0))))</f>
         <v/>
       </c>
@@ -34662,8 +34683,8 @@
       </c>
     </row>
     <row r="60" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="533"/>
-      <c r="B60" s="533"/>
+      <c r="A60" s="539"/>
+      <c r="B60" s="539"/>
       <c r="C60" s="279"/>
       <c r="D60" s="268"/>
       <c r="E60" s="268"/>
@@ -34692,12 +34713,12 @@
         <f ca="1">IF(Q60="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q60/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q60))</f>
         <v/>
       </c>
-      <c r="S60" s="535"/>
-      <c r="T60" s="537"/>
-      <c r="U60" s="539"/>
-      <c r="V60" s="541"/>
-      <c r="W60" s="529"/>
-      <c r="X60" s="531"/>
+      <c r="S60" s="541"/>
+      <c r="T60" s="543"/>
+      <c r="U60" s="553"/>
+      <c r="V60" s="555"/>
+      <c r="W60" s="557"/>
+      <c r="X60" s="559"/>
       <c r="Y60" s="274" t="str">
         <f>IF(B59="","",ROUNDUP(AVERAGE(R60,R60,X59),2))</f>
         <v/>
@@ -34708,10 +34729,10 @@
       </c>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="532">
+      <c r="A61" s="538">
         <v>26</v>
       </c>
-      <c r="B61" s="532" t="str">
+      <c r="B61" s="538" t="str">
         <f>IF('1. Halbjahr'!B29&lt;&gt;"", '1. Halbjahr'!B29, "")</f>
         <v/>
       </c>
@@ -34743,18 +34764,18 @@
         <f ca="1">IF(Q61="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q61/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q61))</f>
         <v/>
       </c>
-      <c r="S61" s="534"/>
-      <c r="T61" s="536"/>
-      <c r="U61" s="538"/>
-      <c r="V61" s="540" t="str">
+      <c r="S61" s="540"/>
+      <c r="T61" s="542"/>
+      <c r="U61" s="552"/>
+      <c r="V61" s="554" t="str">
         <f>IF(B61="","",SUM(S61:U61))</f>
         <v/>
       </c>
-      <c r="W61" s="528" t="str">
+      <c r="W61" s="556" t="str">
         <f>IF(B61="","",IF(ISBLANK(S61),"",IF(AVERAGE(S61:U61)&lt;10,LEFT(AVERAGE(S61:U61),4),LEFT(AVERAGE(S61:U61),5))))</f>
         <v/>
       </c>
-      <c r="X61" s="530" t="str">
+      <c r="X61" s="558" t="str">
         <f>IF(B61="","",IF(W61="","",IF(LEFT(W61,1)="0",0,ROUND(W61,0))))</f>
         <v/>
       </c>
@@ -34768,8 +34789,8 @@
       </c>
     </row>
     <row r="62" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="533"/>
-      <c r="B62" s="533"/>
+      <c r="A62" s="539"/>
+      <c r="B62" s="539"/>
       <c r="C62" s="279"/>
       <c r="D62" s="268"/>
       <c r="E62" s="268"/>
@@ -34798,12 +34819,12 @@
         <f ca="1">IF(Q62="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q62/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q62))</f>
         <v/>
       </c>
-      <c r="S62" s="535"/>
-      <c r="T62" s="537"/>
-      <c r="U62" s="539"/>
-      <c r="V62" s="541"/>
-      <c r="W62" s="529"/>
-      <c r="X62" s="531"/>
+      <c r="S62" s="541"/>
+      <c r="T62" s="543"/>
+      <c r="U62" s="553"/>
+      <c r="V62" s="555"/>
+      <c r="W62" s="557"/>
+      <c r="X62" s="559"/>
       <c r="Y62" s="274" t="str">
         <f>IF(B61="","",ROUNDUP(AVERAGE(R62,R62,X61),2))</f>
         <v/>
@@ -34814,10 +34835,10 @@
       </c>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="532">
+      <c r="A63" s="538">
         <v>27</v>
       </c>
-      <c r="B63" s="532" t="str">
+      <c r="B63" s="538" t="str">
         <f>IF('1. Halbjahr'!B30&lt;&gt;"", '1. Halbjahr'!B30, "")</f>
         <v/>
       </c>
@@ -34849,18 +34870,18 @@
         <f ca="1">IF(Q63="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q63/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q63))</f>
         <v/>
       </c>
-      <c r="S63" s="534"/>
-      <c r="T63" s="536"/>
-      <c r="U63" s="538"/>
-      <c r="V63" s="540" t="str">
+      <c r="S63" s="540"/>
+      <c r="T63" s="542"/>
+      <c r="U63" s="552"/>
+      <c r="V63" s="554" t="str">
         <f>IF(B63="","",SUM(S63:U63))</f>
         <v/>
       </c>
-      <c r="W63" s="528" t="str">
+      <c r="W63" s="556" t="str">
         <f>IF(B63="","",IF(ISBLANK(S63),"",IF(AVERAGE(S63:U63)&lt;10,LEFT(AVERAGE(S63:U63),4),LEFT(AVERAGE(S63:U63),5))))</f>
         <v/>
       </c>
-      <c r="X63" s="530" t="str">
+      <c r="X63" s="558" t="str">
         <f>IF(B63="","",IF(W63="","",IF(LEFT(W63,1)="0",0,ROUND(W63,0))))</f>
         <v/>
       </c>
@@ -34874,8 +34895,8 @@
       </c>
     </row>
     <row r="64" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="533"/>
-      <c r="B64" s="533"/>
+      <c r="A64" s="539"/>
+      <c r="B64" s="539"/>
       <c r="C64" s="279"/>
       <c r="D64" s="268"/>
       <c r="E64" s="268"/>
@@ -34904,12 +34925,12 @@
         <f ca="1">IF(Q64="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q64/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q64))</f>
         <v/>
       </c>
-      <c r="S64" s="535"/>
-      <c r="T64" s="537"/>
-      <c r="U64" s="539"/>
-      <c r="V64" s="541"/>
-      <c r="W64" s="529"/>
-      <c r="X64" s="531"/>
+      <c r="S64" s="541"/>
+      <c r="T64" s="543"/>
+      <c r="U64" s="553"/>
+      <c r="V64" s="555"/>
+      <c r="W64" s="557"/>
+      <c r="X64" s="559"/>
       <c r="Y64" s="274" t="str">
         <f>IF(B63="","",ROUNDUP(AVERAGE(R64,R64,X63),2))</f>
         <v/>
@@ -34920,10 +34941,10 @@
       </c>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="532">
+      <c r="A65" s="538">
         <v>28</v>
       </c>
-      <c r="B65" s="532" t="str">
+      <c r="B65" s="538" t="str">
         <f>IF('1. Halbjahr'!B31&lt;&gt;"", '1. Halbjahr'!B31, "")</f>
         <v/>
       </c>
@@ -34955,18 +34976,18 @@
         <f ca="1">IF(Q65="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q65/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q65))</f>
         <v/>
       </c>
-      <c r="S65" s="534"/>
-      <c r="T65" s="536"/>
-      <c r="U65" s="538"/>
-      <c r="V65" s="540" t="str">
+      <c r="S65" s="540"/>
+      <c r="T65" s="542"/>
+      <c r="U65" s="552"/>
+      <c r="V65" s="554" t="str">
         <f>IF(B65="","",SUM(S65:U65))</f>
         <v/>
       </c>
-      <c r="W65" s="528" t="str">
+      <c r="W65" s="556" t="str">
         <f>IF(B65="","",IF(ISBLANK(S65),"",IF(AVERAGE(S65:U65)&lt;10,LEFT(AVERAGE(S65:U65),4),LEFT(AVERAGE(S65:U65),5))))</f>
         <v/>
       </c>
-      <c r="X65" s="530" t="str">
+      <c r="X65" s="558" t="str">
         <f>IF(B65="","",IF(W65="","",IF(LEFT(W65,1)="0",0,ROUND(W65,0))))</f>
         <v/>
       </c>
@@ -34980,8 +35001,8 @@
       </c>
     </row>
     <row r="66" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="533"/>
-      <c r="B66" s="533"/>
+      <c r="A66" s="539"/>
+      <c r="B66" s="539"/>
       <c r="C66" s="279"/>
       <c r="D66" s="268"/>
       <c r="E66" s="268"/>
@@ -35010,12 +35031,12 @@
         <f ca="1">IF(Q66="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q66/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q66))</f>
         <v/>
       </c>
-      <c r="S66" s="535"/>
-      <c r="T66" s="537"/>
-      <c r="U66" s="539"/>
-      <c r="V66" s="541"/>
-      <c r="W66" s="529"/>
-      <c r="X66" s="531"/>
+      <c r="S66" s="541"/>
+      <c r="T66" s="543"/>
+      <c r="U66" s="553"/>
+      <c r="V66" s="555"/>
+      <c r="W66" s="557"/>
+      <c r="X66" s="559"/>
       <c r="Y66" s="274" t="str">
         <f>IF(B65="","",ROUNDUP(AVERAGE(R66,R66,X65),2))</f>
         <v/>
@@ -35026,10 +35047,10 @@
       </c>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="532">
+      <c r="A67" s="538">
         <v>29</v>
       </c>
-      <c r="B67" s="532" t="str">
+      <c r="B67" s="538" t="str">
         <f>IF('1. Halbjahr'!B32&lt;&gt;"", '1. Halbjahr'!B32, "")</f>
         <v/>
       </c>
@@ -35061,18 +35082,18 @@
         <f ca="1">IF(Q67="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q67/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q67))</f>
         <v/>
       </c>
-      <c r="S67" s="534"/>
-      <c r="T67" s="536"/>
-      <c r="U67" s="538"/>
-      <c r="V67" s="540" t="str">
+      <c r="S67" s="540"/>
+      <c r="T67" s="542"/>
+      <c r="U67" s="552"/>
+      <c r="V67" s="554" t="str">
         <f>IF(B67="","",SUM(S67:U67))</f>
         <v/>
       </c>
-      <c r="W67" s="528" t="str">
+      <c r="W67" s="556" t="str">
         <f>IF(B67="","",IF(ISBLANK(S67),"",IF(AVERAGE(S67:U67)&lt;10,LEFT(AVERAGE(S67:U67),4),LEFT(AVERAGE(S67:U67),5))))</f>
         <v/>
       </c>
-      <c r="X67" s="530" t="str">
+      <c r="X67" s="558" t="str">
         <f>IF(B67="","",IF(W67="","",IF(LEFT(W67,1)="0",0,ROUND(W67,0))))</f>
         <v/>
       </c>
@@ -35086,8 +35107,8 @@
       </c>
     </row>
     <row r="68" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="533"/>
-      <c r="B68" s="533"/>
+      <c r="A68" s="539"/>
+      <c r="B68" s="539"/>
       <c r="C68" s="279"/>
       <c r="D68" s="268"/>
       <c r="E68" s="268"/>
@@ -35116,12 +35137,12 @@
         <f ca="1">IF(Q68="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q68/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q68))</f>
         <v/>
       </c>
-      <c r="S68" s="535"/>
-      <c r="T68" s="537"/>
-      <c r="U68" s="539"/>
-      <c r="V68" s="541"/>
-      <c r="W68" s="529"/>
-      <c r="X68" s="531"/>
+      <c r="S68" s="541"/>
+      <c r="T68" s="543"/>
+      <c r="U68" s="553"/>
+      <c r="V68" s="555"/>
+      <c r="W68" s="557"/>
+      <c r="X68" s="559"/>
       <c r="Y68" s="274" t="str">
         <f>IF(B67="","",ROUNDUP(AVERAGE(R68,R68,X67),2))</f>
         <v/>
@@ -35132,10 +35153,10 @@
       </c>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="532">
+      <c r="A69" s="538">
         <v>30</v>
       </c>
-      <c r="B69" s="532" t="str">
+      <c r="B69" s="538" t="str">
         <f>IF('1. Halbjahr'!B33&lt;&gt;"", '1. Halbjahr'!B33, "")</f>
         <v/>
       </c>
@@ -35167,18 +35188,18 @@
         <f ca="1">IF(Q69="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q69/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q69))</f>
         <v/>
       </c>
-      <c r="S69" s="534"/>
-      <c r="T69" s="536"/>
-      <c r="U69" s="538"/>
-      <c r="V69" s="540" t="str">
+      <c r="S69" s="540"/>
+      <c r="T69" s="542"/>
+      <c r="U69" s="552"/>
+      <c r="V69" s="554" t="str">
         <f>IF(B69="","",SUM(S69:U69))</f>
         <v/>
       </c>
-      <c r="W69" s="528" t="str">
+      <c r="W69" s="556" t="str">
         <f>IF(B69="","",IF(ISBLANK(S69),"",IF(AVERAGE(S69:U69)&lt;10,LEFT(AVERAGE(S69:U69),4),LEFT(AVERAGE(S69:U69),5))))</f>
         <v/>
       </c>
-      <c r="X69" s="530" t="str">
+      <c r="X69" s="558" t="str">
         <f>IF(B69="","",IF(W69="","",IF(LEFT(W69,1)="0",0,ROUND(W69,0))))</f>
         <v/>
       </c>
@@ -35192,8 +35213,8 @@
       </c>
     </row>
     <row r="70" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="533"/>
-      <c r="B70" s="533"/>
+      <c r="A70" s="539"/>
+      <c r="B70" s="539"/>
       <c r="C70" s="279"/>
       <c r="D70" s="268"/>
       <c r="E70" s="268"/>
@@ -35222,12 +35243,12 @@
         <f ca="1">IF(Q70="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q70/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q70))</f>
         <v/>
       </c>
-      <c r="S70" s="535"/>
-      <c r="T70" s="537"/>
-      <c r="U70" s="539"/>
-      <c r="V70" s="541"/>
-      <c r="W70" s="529"/>
-      <c r="X70" s="531"/>
+      <c r="S70" s="541"/>
+      <c r="T70" s="543"/>
+      <c r="U70" s="553"/>
+      <c r="V70" s="555"/>
+      <c r="W70" s="557"/>
+      <c r="X70" s="559"/>
       <c r="Y70" s="274" t="str">
         <f>IF(B69="","",ROUNDUP(AVERAGE(R70,R70,X69),2))</f>
         <v/>
@@ -35238,10 +35259,10 @@
       </c>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="532">
+      <c r="A71" s="538">
         <v>31</v>
       </c>
-      <c r="B71" s="532" t="str">
+      <c r="B71" s="538" t="str">
         <f>IF('1. Halbjahr'!B34&lt;&gt;"", '1. Halbjahr'!B34, "")</f>
         <v/>
       </c>
@@ -35273,18 +35294,18 @@
         <f ca="1">IF(Q71="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q71/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q71))</f>
         <v/>
       </c>
-      <c r="S71" s="534"/>
-      <c r="T71" s="536"/>
-      <c r="U71" s="538"/>
-      <c r="V71" s="540" t="str">
+      <c r="S71" s="540"/>
+      <c r="T71" s="542"/>
+      <c r="U71" s="552"/>
+      <c r="V71" s="554" t="str">
         <f>IF(B71="","",SUM(S71:U71))</f>
         <v/>
       </c>
-      <c r="W71" s="528" t="str">
+      <c r="W71" s="556" t="str">
         <f>IF(B71="","",IF(ISBLANK(S71),"",IF(AVERAGE(S71:U71)&lt;10,LEFT(AVERAGE(S71:U71),4),LEFT(AVERAGE(S71:U71),5))))</f>
         <v/>
       </c>
-      <c r="X71" s="530" t="str">
+      <c r="X71" s="558" t="str">
         <f>IF(B71="","",IF(W71="","",IF(LEFT(W71,1)="0",0,ROUND(W71,0))))</f>
         <v/>
       </c>
@@ -35298,8 +35319,8 @@
       </c>
     </row>
     <row r="72" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="533"/>
-      <c r="B72" s="533"/>
+      <c r="A72" s="539"/>
+      <c r="B72" s="539"/>
       <c r="C72" s="279"/>
       <c r="D72" s="268"/>
       <c r="E72" s="268"/>
@@ -35328,12 +35349,12 @@
         <f ca="1">IF(Q72="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q72/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q72))</f>
         <v/>
       </c>
-      <c r="S72" s="535"/>
-      <c r="T72" s="537"/>
-      <c r="U72" s="539"/>
-      <c r="V72" s="541"/>
-      <c r="W72" s="529"/>
-      <c r="X72" s="531"/>
+      <c r="S72" s="541"/>
+      <c r="T72" s="543"/>
+      <c r="U72" s="553"/>
+      <c r="V72" s="555"/>
+      <c r="W72" s="557"/>
+      <c r="X72" s="559"/>
       <c r="Y72" s="274" t="str">
         <f>IF(B71="","",ROUNDUP(AVERAGE(R72,R72,X71),2))</f>
         <v/>
@@ -35344,10 +35365,10 @@
       </c>
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="532">
+      <c r="A73" s="538">
         <v>32</v>
       </c>
-      <c r="B73" s="532" t="str">
+      <c r="B73" s="538" t="str">
         <f>IF('1. Halbjahr'!B35&lt;&gt;"", '1. Halbjahr'!B35, "")</f>
         <v/>
       </c>
@@ -35379,18 +35400,18 @@
         <f ca="1">IF(Q73="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q73/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q73))</f>
         <v/>
       </c>
-      <c r="S73" s="534"/>
-      <c r="T73" s="536"/>
-      <c r="U73" s="538"/>
-      <c r="V73" s="540" t="str">
+      <c r="S73" s="540"/>
+      <c r="T73" s="542"/>
+      <c r="U73" s="552"/>
+      <c r="V73" s="554" t="str">
         <f>IF(B73="","",SUM(S73:U73))</f>
         <v/>
       </c>
-      <c r="W73" s="528" t="str">
+      <c r="W73" s="556" t="str">
         <f>IF(B73="","",IF(ISBLANK(S73),"",IF(AVERAGE(S73:U73)&lt;10,LEFT(AVERAGE(S73:U73),4),LEFT(AVERAGE(S73:U73),5))))</f>
         <v/>
       </c>
-      <c r="X73" s="530" t="str">
+      <c r="X73" s="558" t="str">
         <f>IF(B73="","",IF(W73="","",IF(LEFT(W73,1)="0",0,ROUND(W73,0))))</f>
         <v/>
       </c>
@@ -35404,8 +35425,8 @@
       </c>
     </row>
     <row r="74" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="533"/>
-      <c r="B74" s="533"/>
+      <c r="A74" s="539"/>
+      <c r="B74" s="539"/>
       <c r="C74" s="279"/>
       <c r="D74" s="268"/>
       <c r="E74" s="268"/>
@@ -35434,12 +35455,12 @@
         <f ca="1">IF(Q74="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q74/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q74))</f>
         <v/>
       </c>
-      <c r="S74" s="535"/>
-      <c r="T74" s="537"/>
-      <c r="U74" s="539"/>
-      <c r="V74" s="541"/>
-      <c r="W74" s="529"/>
-      <c r="X74" s="531"/>
+      <c r="S74" s="541"/>
+      <c r="T74" s="543"/>
+      <c r="U74" s="553"/>
+      <c r="V74" s="555"/>
+      <c r="W74" s="557"/>
+      <c r="X74" s="559"/>
       <c r="Y74" s="274" t="str">
         <f>IF(B73="","",ROUNDUP(AVERAGE(R74,R74,X73),2))</f>
         <v/>
@@ -35450,10 +35471,10 @@
       </c>
     </row>
     <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="532">
+      <c r="A75" s="538">
         <v>33</v>
       </c>
-      <c r="B75" s="532" t="str">
+      <c r="B75" s="538" t="str">
         <f>IF('1. Halbjahr'!B36&lt;&gt;"", '1. Halbjahr'!B36, "")</f>
         <v/>
       </c>
@@ -35485,18 +35506,18 @@
         <f ca="1">IF(Q75="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q75/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q75))</f>
         <v/>
       </c>
-      <c r="S75" s="534"/>
-      <c r="T75" s="536"/>
-      <c r="U75" s="538"/>
-      <c r="V75" s="540" t="str">
+      <c r="S75" s="540"/>
+      <c r="T75" s="542"/>
+      <c r="U75" s="552"/>
+      <c r="V75" s="554" t="str">
         <f>IF(B75="","",SUM(S75:U75))</f>
         <v/>
       </c>
-      <c r="W75" s="528" t="str">
+      <c r="W75" s="556" t="str">
         <f>IF(B75="","",IF(ISBLANK(S75),"",IF(AVERAGE(S75:U75)&lt;10,LEFT(AVERAGE(S75:U75),4),LEFT(AVERAGE(S75:U75),5))))</f>
         <v/>
       </c>
-      <c r="X75" s="530" t="str">
+      <c r="X75" s="558" t="str">
         <f>IF(B75="","",IF(W75="","",IF(LEFT(W75,1)="0",0,ROUND(W75,0))))</f>
         <v/>
       </c>
@@ -35510,8 +35531,8 @@
       </c>
     </row>
     <row r="76" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="533"/>
-      <c r="B76" s="533"/>
+      <c r="A76" s="539"/>
+      <c r="B76" s="539"/>
       <c r="C76" s="279"/>
       <c r="D76" s="268"/>
       <c r="E76" s="268"/>
@@ -35540,12 +35561,12 @@
         <f ca="1">IF(Q76="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q76/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q76))</f>
         <v/>
       </c>
-      <c r="S76" s="535"/>
-      <c r="T76" s="537"/>
-      <c r="U76" s="539"/>
-      <c r="V76" s="541"/>
-      <c r="W76" s="529"/>
-      <c r="X76" s="531"/>
+      <c r="S76" s="541"/>
+      <c r="T76" s="543"/>
+      <c r="U76" s="553"/>
+      <c r="V76" s="555"/>
+      <c r="W76" s="557"/>
+      <c r="X76" s="559"/>
       <c r="Y76" s="274" t="str">
         <f>IF(B75="","",ROUNDUP(AVERAGE(R76,R76,X75),2))</f>
         <v/>
@@ -35556,10 +35577,10 @@
       </c>
     </row>
     <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="532">
+      <c r="A77" s="538">
         <v>34</v>
       </c>
-      <c r="B77" s="532" t="str">
+      <c r="B77" s="538" t="str">
         <f>IF('1. Halbjahr'!B37&lt;&gt;"", '1. Halbjahr'!B37, "")</f>
         <v/>
       </c>
@@ -35591,18 +35612,18 @@
         <f ca="1">IF(Q77="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q77/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q77))</f>
         <v/>
       </c>
-      <c r="S77" s="534"/>
-      <c r="T77" s="536"/>
-      <c r="U77" s="538"/>
-      <c r="V77" s="540" t="str">
+      <c r="S77" s="540"/>
+      <c r="T77" s="542"/>
+      <c r="U77" s="552"/>
+      <c r="V77" s="554" t="str">
         <f>IF(B77="","",SUM(S77:U77))</f>
         <v/>
       </c>
-      <c r="W77" s="528" t="str">
+      <c r="W77" s="556" t="str">
         <f>IF(B77="","",IF(ISBLANK(S77),"",IF(AVERAGE(S77:U77)&lt;10,LEFT(AVERAGE(S77:U77),4),LEFT(AVERAGE(S77:U77),5))))</f>
         <v/>
       </c>
-      <c r="X77" s="530" t="str">
+      <c r="X77" s="558" t="str">
         <f>IF(B77="","",IF(W77="","",IF(LEFT(W77,1)="0",0,ROUND(W77,0))))</f>
         <v/>
       </c>
@@ -35616,8 +35637,8 @@
       </c>
     </row>
     <row r="78" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="533"/>
-      <c r="B78" s="533"/>
+      <c r="A78" s="539"/>
+      <c r="B78" s="539"/>
       <c r="C78" s="279"/>
       <c r="D78" s="268"/>
       <c r="E78" s="268"/>
@@ -35646,12 +35667,12 @@
         <f ca="1">IF(Q78="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q78/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q78))</f>
         <v/>
       </c>
-      <c r="S78" s="542"/>
-      <c r="T78" s="543"/>
-      <c r="U78" s="544"/>
-      <c r="V78" s="545"/>
-      <c r="W78" s="529"/>
-      <c r="X78" s="531"/>
+      <c r="S78" s="560"/>
+      <c r="T78" s="561"/>
+      <c r="U78" s="562"/>
+      <c r="V78" s="563"/>
+      <c r="W78" s="557"/>
+      <c r="X78" s="559"/>
       <c r="Y78" s="287" t="str">
         <f>IF(B77="","",ROUNDUP(AVERAGE(R78,R78,X77),2))</f>
         <v/>
@@ -35662,10 +35683,10 @@
       </c>
     </row>
     <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="532">
+      <c r="A79" s="538">
         <v>35</v>
       </c>
-      <c r="B79" s="532" t="str">
+      <c r="B79" s="538" t="str">
         <f>IF('1. Halbjahr'!B38&lt;&gt;"", '1. Halbjahr'!B38, "")</f>
         <v/>
       </c>
@@ -35697,18 +35718,18 @@
         <f ca="1">IF(Q79="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q79/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q79))</f>
         <v/>
       </c>
-      <c r="S79" s="534"/>
-      <c r="T79" s="536"/>
-      <c r="U79" s="538"/>
-      <c r="V79" s="540" t="str">
+      <c r="S79" s="540"/>
+      <c r="T79" s="542"/>
+      <c r="U79" s="552"/>
+      <c r="V79" s="554" t="str">
         <f>IF(B79="","",SUM(S79:U79))</f>
         <v/>
       </c>
-      <c r="W79" s="528" t="str">
+      <c r="W79" s="556" t="str">
         <f>IF(B79="","",IF(ISBLANK(S79),"",IF(AVERAGE(S79:U79)&lt;10,LEFT(AVERAGE(S79:U79),4),LEFT(AVERAGE(S79:U79),5))))</f>
         <v/>
       </c>
-      <c r="X79" s="530" t="str">
+      <c r="X79" s="558" t="str">
         <f>IF(B79="","",IF(W79="","",IF(LEFT(W79,1)="0",0,ROUND(W79,0))))</f>
         <v/>
       </c>
@@ -35722,8 +35743,8 @@
       </c>
     </row>
     <row r="80" spans="1:26" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="533"/>
-      <c r="B80" s="533"/>
+      <c r="A80" s="539"/>
+      <c r="B80" s="539"/>
       <c r="C80" s="284"/>
       <c r="D80" s="285"/>
       <c r="E80" s="285"/>
@@ -35752,12 +35773,12 @@
         <f ca="1">IF(Q80="","",IF(AP!$E$42="BE",INDIRECT("AP!P"&amp;MATCH(100*Q80/AP!$E$44,AP!$Q$4:$Q$20,-1)+4),Q80))</f>
         <v/>
       </c>
-      <c r="S80" s="535"/>
-      <c r="T80" s="537"/>
-      <c r="U80" s="539"/>
-      <c r="V80" s="541"/>
-      <c r="W80" s="529"/>
-      <c r="X80" s="531"/>
+      <c r="S80" s="541"/>
+      <c r="T80" s="543"/>
+      <c r="U80" s="553"/>
+      <c r="V80" s="555"/>
+      <c r="W80" s="557"/>
+      <c r="X80" s="559"/>
       <c r="Y80" s="274" t="str">
         <f>IF(B79="","",ROUNDUP(AVERAGE(R80,R80,X79),2))</f>
         <v/>
@@ -35786,6 +35807,278 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="MP4p+miPz8A/zV+W16Agbly2yeiPfRWRuPYG2PSyyMmyhwIWDBl5r2fJsl74iX77TgYMFZs024fYqdx3rIlvkw==" saltValue="G2QpsDcpT+qU3FqHOHn5ZA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="288">
+    <mergeCell ref="W77:W78"/>
+    <mergeCell ref="X77:X78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="S79:S80"/>
+    <mergeCell ref="T79:T80"/>
+    <mergeCell ref="U79:U80"/>
+    <mergeCell ref="V79:V80"/>
+    <mergeCell ref="W79:W80"/>
+    <mergeCell ref="X79:X80"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="S77:S78"/>
+    <mergeCell ref="T77:T78"/>
+    <mergeCell ref="U77:U78"/>
+    <mergeCell ref="V77:V78"/>
+    <mergeCell ref="W73:W74"/>
+    <mergeCell ref="X73:X74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="S75:S76"/>
+    <mergeCell ref="T75:T76"/>
+    <mergeCell ref="U75:U76"/>
+    <mergeCell ref="V75:V76"/>
+    <mergeCell ref="W75:W76"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="S73:S74"/>
+    <mergeCell ref="T73:T74"/>
+    <mergeCell ref="U73:U74"/>
+    <mergeCell ref="V73:V74"/>
+    <mergeCell ref="W69:W70"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="S71:S72"/>
+    <mergeCell ref="T71:T72"/>
+    <mergeCell ref="U71:U72"/>
+    <mergeCell ref="V71:V72"/>
+    <mergeCell ref="W71:W72"/>
+    <mergeCell ref="X71:X72"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="S69:S70"/>
+    <mergeCell ref="T69:T70"/>
+    <mergeCell ref="U69:U70"/>
+    <mergeCell ref="V69:V70"/>
+    <mergeCell ref="W65:W66"/>
+    <mergeCell ref="X65:X66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="S67:S68"/>
+    <mergeCell ref="T67:T68"/>
+    <mergeCell ref="U67:U68"/>
+    <mergeCell ref="V67:V68"/>
+    <mergeCell ref="W67:W68"/>
+    <mergeCell ref="X67:X68"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="S65:S66"/>
+    <mergeCell ref="T65:T66"/>
+    <mergeCell ref="U65:U66"/>
+    <mergeCell ref="V65:V66"/>
+    <mergeCell ref="W61:W62"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="S63:S64"/>
+    <mergeCell ref="T63:T64"/>
+    <mergeCell ref="U63:U64"/>
+    <mergeCell ref="V63:V64"/>
+    <mergeCell ref="W63:W64"/>
+    <mergeCell ref="X63:X64"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="S61:S62"/>
+    <mergeCell ref="T61:T62"/>
+    <mergeCell ref="U61:U62"/>
+    <mergeCell ref="V61:V62"/>
+    <mergeCell ref="W57:W58"/>
+    <mergeCell ref="X57:X58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="S59:S60"/>
+    <mergeCell ref="T59:T60"/>
+    <mergeCell ref="U59:U60"/>
+    <mergeCell ref="V59:V60"/>
+    <mergeCell ref="W59:W60"/>
+    <mergeCell ref="X59:X60"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="S57:S58"/>
+    <mergeCell ref="T57:T58"/>
+    <mergeCell ref="U57:U58"/>
+    <mergeCell ref="V57:V58"/>
+    <mergeCell ref="W53:W54"/>
+    <mergeCell ref="X53:X54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="S55:S56"/>
+    <mergeCell ref="T55:T56"/>
+    <mergeCell ref="U55:U56"/>
+    <mergeCell ref="V55:V56"/>
+    <mergeCell ref="W55:W56"/>
+    <mergeCell ref="X55:X56"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="S53:S54"/>
+    <mergeCell ref="T53:T54"/>
+    <mergeCell ref="U53:U54"/>
+    <mergeCell ref="V53:V54"/>
+    <mergeCell ref="W49:W50"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:T52"/>
+    <mergeCell ref="U51:U52"/>
+    <mergeCell ref="V51:V52"/>
+    <mergeCell ref="W51:W52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="T49:T50"/>
+    <mergeCell ref="U49:U50"/>
+    <mergeCell ref="V49:V50"/>
+    <mergeCell ref="W45:W46"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="S47:S48"/>
+    <mergeCell ref="T47:T48"/>
+    <mergeCell ref="U47:U48"/>
+    <mergeCell ref="V47:V48"/>
+    <mergeCell ref="W47:W48"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="S45:S46"/>
+    <mergeCell ref="T45:T46"/>
+    <mergeCell ref="U45:U46"/>
+    <mergeCell ref="V45:V46"/>
+    <mergeCell ref="W41:W42"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="U43:U44"/>
+    <mergeCell ref="V43:V44"/>
+    <mergeCell ref="W43:W44"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="U41:U42"/>
+    <mergeCell ref="V41:V42"/>
+    <mergeCell ref="W37:W38"/>
+    <mergeCell ref="X37:X38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="U39:U40"/>
+    <mergeCell ref="V39:V40"/>
+    <mergeCell ref="W39:W40"/>
+    <mergeCell ref="X39:X40"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="U37:U38"/>
+    <mergeCell ref="V37:V38"/>
+    <mergeCell ref="W33:W34"/>
+    <mergeCell ref="X33:X34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="U35:U36"/>
+    <mergeCell ref="V35:V36"/>
+    <mergeCell ref="W35:W36"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="U33:U34"/>
+    <mergeCell ref="V33:V34"/>
+    <mergeCell ref="W29:W30"/>
+    <mergeCell ref="X29:X30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="U31:U32"/>
+    <mergeCell ref="V31:V32"/>
+    <mergeCell ref="W31:W32"/>
+    <mergeCell ref="X31:X32"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="U29:U30"/>
+    <mergeCell ref="V29:V30"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="W27:W28"/>
+    <mergeCell ref="X27:X28"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="W21:W22"/>
+    <mergeCell ref="X21:X22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="U23:U24"/>
+    <mergeCell ref="V23:V24"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:X24"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="U21:U22"/>
+    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="X15:X16"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="M8:O8"/>
     <mergeCell ref="A11:A12"/>
@@ -35802,278 +36095,6 @@
     <mergeCell ref="V11:V12"/>
     <mergeCell ref="W11:W12"/>
     <mergeCell ref="X11:X12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="U15:U16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="X19:X20"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="W21:W22"/>
-    <mergeCell ref="X21:X22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="U23:U24"/>
-    <mergeCell ref="V23:V24"/>
-    <mergeCell ref="W23:W24"/>
-    <mergeCell ref="X23:X24"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="U21:U22"/>
-    <mergeCell ref="V21:V22"/>
-    <mergeCell ref="W25:W26"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="W27:W28"/>
-    <mergeCell ref="X27:X28"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="U25:U26"/>
-    <mergeCell ref="V25:V26"/>
-    <mergeCell ref="W29:W30"/>
-    <mergeCell ref="X29:X30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="U31:U32"/>
-    <mergeCell ref="V31:V32"/>
-    <mergeCell ref="W31:W32"/>
-    <mergeCell ref="X31:X32"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="U29:U30"/>
-    <mergeCell ref="V29:V30"/>
-    <mergeCell ref="W33:W34"/>
-    <mergeCell ref="X33:X34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="S35:S36"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="U35:U36"/>
-    <mergeCell ref="V35:V36"/>
-    <mergeCell ref="W35:W36"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="T33:T34"/>
-    <mergeCell ref="U33:U34"/>
-    <mergeCell ref="V33:V34"/>
-    <mergeCell ref="W37:W38"/>
-    <mergeCell ref="X37:X38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="U39:U40"/>
-    <mergeCell ref="V39:V40"/>
-    <mergeCell ref="W39:W40"/>
-    <mergeCell ref="X39:X40"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="U37:U38"/>
-    <mergeCell ref="V37:V38"/>
-    <mergeCell ref="W41:W42"/>
-    <mergeCell ref="X41:X42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="S43:S44"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="U43:U44"/>
-    <mergeCell ref="V43:V44"/>
-    <mergeCell ref="W43:W44"/>
-    <mergeCell ref="X43:X44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="U41:U42"/>
-    <mergeCell ref="V41:V42"/>
-    <mergeCell ref="W45:W46"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="T47:T48"/>
-    <mergeCell ref="U47:U48"/>
-    <mergeCell ref="V47:V48"/>
-    <mergeCell ref="W47:W48"/>
-    <mergeCell ref="X47:X48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="S45:S46"/>
-    <mergeCell ref="T45:T46"/>
-    <mergeCell ref="U45:U46"/>
-    <mergeCell ref="V45:V46"/>
-    <mergeCell ref="W49:W50"/>
-    <mergeCell ref="X49:X50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="S51:S52"/>
-    <mergeCell ref="T51:T52"/>
-    <mergeCell ref="U51:U52"/>
-    <mergeCell ref="V51:V52"/>
-    <mergeCell ref="W51:W52"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="S49:S50"/>
-    <mergeCell ref="T49:T50"/>
-    <mergeCell ref="U49:U50"/>
-    <mergeCell ref="V49:V50"/>
-    <mergeCell ref="W53:W54"/>
-    <mergeCell ref="X53:X54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="S55:S56"/>
-    <mergeCell ref="T55:T56"/>
-    <mergeCell ref="U55:U56"/>
-    <mergeCell ref="V55:V56"/>
-    <mergeCell ref="W55:W56"/>
-    <mergeCell ref="X55:X56"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="S53:S54"/>
-    <mergeCell ref="T53:T54"/>
-    <mergeCell ref="U53:U54"/>
-    <mergeCell ref="V53:V54"/>
-    <mergeCell ref="W57:W58"/>
-    <mergeCell ref="X57:X58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="S59:S60"/>
-    <mergeCell ref="T59:T60"/>
-    <mergeCell ref="U59:U60"/>
-    <mergeCell ref="V59:V60"/>
-    <mergeCell ref="W59:W60"/>
-    <mergeCell ref="X59:X60"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="S57:S58"/>
-    <mergeCell ref="T57:T58"/>
-    <mergeCell ref="U57:U58"/>
-    <mergeCell ref="V57:V58"/>
-    <mergeCell ref="W61:W62"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="S63:S64"/>
-    <mergeCell ref="T63:T64"/>
-    <mergeCell ref="U63:U64"/>
-    <mergeCell ref="V63:V64"/>
-    <mergeCell ref="W63:W64"/>
-    <mergeCell ref="X63:X64"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="S61:S62"/>
-    <mergeCell ref="T61:T62"/>
-    <mergeCell ref="U61:U62"/>
-    <mergeCell ref="V61:V62"/>
-    <mergeCell ref="W65:W66"/>
-    <mergeCell ref="X65:X66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="S67:S68"/>
-    <mergeCell ref="T67:T68"/>
-    <mergeCell ref="U67:U68"/>
-    <mergeCell ref="V67:V68"/>
-    <mergeCell ref="W67:W68"/>
-    <mergeCell ref="X67:X68"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="S65:S66"/>
-    <mergeCell ref="T65:T66"/>
-    <mergeCell ref="U65:U66"/>
-    <mergeCell ref="V65:V66"/>
-    <mergeCell ref="W69:W70"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="S71:S72"/>
-    <mergeCell ref="T71:T72"/>
-    <mergeCell ref="U71:U72"/>
-    <mergeCell ref="V71:V72"/>
-    <mergeCell ref="W71:W72"/>
-    <mergeCell ref="X71:X72"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="S69:S70"/>
-    <mergeCell ref="T69:T70"/>
-    <mergeCell ref="U69:U70"/>
-    <mergeCell ref="V69:V70"/>
-    <mergeCell ref="W73:W74"/>
-    <mergeCell ref="X73:X74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="S75:S76"/>
-    <mergeCell ref="T75:T76"/>
-    <mergeCell ref="U75:U76"/>
-    <mergeCell ref="V75:V76"/>
-    <mergeCell ref="W75:W76"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="S73:S74"/>
-    <mergeCell ref="T73:T74"/>
-    <mergeCell ref="U73:U74"/>
-    <mergeCell ref="V73:V74"/>
-    <mergeCell ref="W77:W78"/>
-    <mergeCell ref="X77:X78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="S79:S80"/>
-    <mergeCell ref="T79:T80"/>
-    <mergeCell ref="U79:U80"/>
-    <mergeCell ref="V79:V80"/>
-    <mergeCell ref="W79:W80"/>
-    <mergeCell ref="X79:X80"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="S77:S78"/>
-    <mergeCell ref="T77:T78"/>
-    <mergeCell ref="U77:U78"/>
-    <mergeCell ref="V77:V78"/>
   </mergeCells>
   <conditionalFormatting sqref="C11 C15 C17 C19 C21 C23 C25 C27 C29 C31 C33 C35 C37 C39 C41 C43 C45 C47 C49 C51 C53 C55 C57 C59 C61 C63 C65 C67 C69 C71 C73 C75 C77 C79">
     <cfRule type="cellIs" dxfId="37" priority="21" stopIfTrue="1" operator="greaterThan">
@@ -36795,17 +36816,17 @@
       <c r="B1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -36921,11 +36942,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -38239,48 +38260,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -38699,17 +38720,17 @@
       <c r="B1" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -38825,11 +38846,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -40143,48 +40164,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -40603,17 +40624,17 @@
       <c r="B1" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -40729,11 +40750,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -42047,48 +42068,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -42507,17 +42528,17 @@
       <c r="B1" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -42633,11 +42654,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -43951,48 +43972,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -44411,17 +44432,17 @@
       <c r="B1" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -44537,11 +44558,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -45855,48 +45876,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -46315,17 +46336,17 @@
       <c r="B1" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="453" t="str">
+      <c r="C1" s="466" t="str">
         <f>IF('1. Halbjahr'!E1="","",'1. Halbjahr'!E1)</f>
         <v/>
       </c>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
+      <c r="D1" s="466"/>
+      <c r="E1" s="466"/>
       <c r="F1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="451"/>
-      <c r="H1" s="452"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="465"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
       <c r="K1" s="42"/>
@@ -46441,11 +46462,11 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="462" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="450"/>
-      <c r="H5" s="450"/>
+      <c r="G5" s="463"/>
+      <c r="H5" s="463"/>
       <c r="I5" s="1"/>
       <c r="J5" s="47" t="str">
         <f t="shared" si="0"/>
@@ -47759,48 +47780,48 @@
     </row>
     <row r="39" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="446"/>
+      <c r="A40" s="459"/>
       <c r="B40" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="454" t="s">
+      <c r="C40" s="467" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="455"/>
-      <c r="E40" s="458" t="s">
+      <c r="D40" s="468"/>
+      <c r="E40" s="471" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="458"/>
-      <c r="G40" s="459"/>
+      <c r="F40" s="471"/>
+      <c r="G40" s="472"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="447"/>
+      <c r="A41" s="460"/>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="456" t="s">
+      <c r="C41" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="457"/>
-      <c r="E41" s="460" t="s">
+      <c r="D41" s="470"/>
+      <c r="E41" s="473" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="460"/>
-      <c r="G41" s="461"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="448"/>
+      <c r="A42" s="461"/>
       <c r="C42" s="67" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="460" t="s">
+      <c r="E42" s="473" t="s">
         <v>112</v>
       </c>
-      <c r="F42" s="460"/>
-      <c r="G42" s="461"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="442"/>
@@ -48222,34 +48243,34 @@
         <v>33</v>
       </c>
       <c r="D1" s="383"/>
-      <c r="E1" s="479">
+      <c r="E1" s="482">
         <f>'1. Halbjahr'!E1:H1</f>
         <v>0</v>
       </c>
-      <c r="F1" s="479"/>
-      <c r="G1" s="479"/>
-      <c r="H1" s="480"/>
-      <c r="I1" s="472" t="str">
+      <c r="F1" s="482"/>
+      <c r="G1" s="482"/>
+      <c r="H1" s="483"/>
+      <c r="I1" s="475" t="str">
         <f>'1. Halbjahr'!I1:J1</f>
         <v>Lehrer/in:</v>
       </c>
-      <c r="J1" s="473"/>
-      <c r="K1" s="479">
+      <c r="J1" s="476"/>
+      <c r="K1" s="482">
         <f>'1. Halbjahr'!K1:L1</f>
         <v>0</v>
       </c>
-      <c r="L1" s="480"/>
+      <c r="L1" s="483"/>
       <c r="M1" s="383" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="474">
+      <c r="N1" s="477">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
-      </c>
-      <c r="O1" s="475"/>
+        <v>46296</v>
+      </c>
+      <c r="O1" s="478"/>
       <c r="P1" s="383"/>
-      <c r="Q1" s="559"/>
-      <c r="R1" s="559"/>
+      <c r="Q1" s="446"/>
+      <c r="R1" s="446"/>
       <c r="S1" s="384"/>
       <c r="T1" s="384"/>
       <c r="U1" s="384"/>
@@ -48273,26 +48294,26 @@
       <c r="B2" s="392" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="476" t="s">
+      <c r="C2" s="479" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="477"/>
-      <c r="E2" s="477"/>
-      <c r="F2" s="477"/>
-      <c r="G2" s="477"/>
-      <c r="H2" s="477"/>
-      <c r="I2" s="477"/>
-      <c r="J2" s="477"/>
-      <c r="K2" s="477"/>
-      <c r="L2" s="477"/>
-      <c r="M2" s="477"/>
-      <c r="N2" s="477"/>
-      <c r="O2" s="478"/>
-      <c r="P2" s="561"/>
-      <c r="Q2" s="562" t="s">
+      <c r="D2" s="480"/>
+      <c r="E2" s="480"/>
+      <c r="F2" s="480"/>
+      <c r="G2" s="480"/>
+      <c r="H2" s="480"/>
+      <c r="I2" s="480"/>
+      <c r="J2" s="480"/>
+      <c r="K2" s="480"/>
+      <c r="L2" s="480"/>
+      <c r="M2" s="480"/>
+      <c r="N2" s="480"/>
+      <c r="O2" s="481"/>
+      <c r="P2" s="448"/>
+      <c r="Q2" s="484" t="s">
         <v>85</v>
       </c>
-      <c r="R2" s="563"/>
+      <c r="R2" s="485"/>
       <c r="S2" s="384"/>
       <c r="T2" s="384"/>
       <c r="U2" s="384"/>
@@ -48357,7 +48378,7 @@
       <c r="Q3" s="316" t="s">
         <v>83</v>
       </c>
-      <c r="R3" s="560" t="s">
+      <c r="R3" s="447" t="s">
         <v>84</v>
       </c>
       <c r="S3" s="384"/>
